--- a/정기/BM/각성 절멸타 수치/각성 절멸타 수치.xlsx
+++ b/정기/BM/각성 절멸타 수치/각성 절멸타 수치.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\BM\각성 절멸타 수치\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC666D72-0599-4EBA-92CB-817AE2B6C5E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694A4C8D-B188-442A-80BD-7E7DE9A575FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{3E321328-0C01-4213-932A-34E838058470}"/>
+    <workbookView xWindow="15495" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{3E321328-0C01-4213-932A-34E838058470}"/>
   </bookViews>
   <sheets>
     <sheet name="보스체력" sheetId="2" r:id="rId1"/>
@@ -471,7 +471,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0.000%"/>
-    <numFmt numFmtId="178" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -590,10 +590,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2731,33 +2731,33 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="E15">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
         <f t="shared" si="4"/>
-        <v>3010</v>
+        <v>3870</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>1.0134680134680134</v>
+        <v>1.303030303030303</v>
       </c>
       <c r="J15">
         <f t="shared" si="0"/>
-        <v>1255703</v>
+        <v>1275703</v>
       </c>
       <c r="K15">
         <f t="shared" si="2"/>
-        <v>1.1356602993751486</v>
+        <v>1.1537483392918351</v>
       </c>
       <c r="M15">
         <f t="shared" si="3"/>
-        <v>1.1509553875822212</v>
+        <v>1.5033690481681488</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -2771,33 +2771,33 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="E16">
-        <v>40</v>
+        <v>1200</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
         <f t="shared" si="4"/>
-        <v>3050</v>
+        <v>5070</v>
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>1.0132890365448506</v>
+        <v>1.3100775193798451</v>
       </c>
       <c r="J16">
         <f t="shared" si="0"/>
-        <v>1405703</v>
+        <v>1475703</v>
       </c>
       <c r="K16">
         <f t="shared" si="2"/>
-        <v>1.1194549985147761</v>
+        <v>1.1567763029482567</v>
       </c>
       <c r="M16">
         <f t="shared" si="3"/>
-        <v>1.1343314769003547</v>
+        <v>1.5154666294438404</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -2811,33 +2811,33 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>150000</v>
+        <v>230000</v>
       </c>
       <c r="E17">
-        <v>40</v>
+        <v>1600</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17">
         <f t="shared" si="4"/>
-        <v>3090</v>
+        <v>6670</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>1.0131147540983607</v>
+        <v>1.3155818540433926</v>
       </c>
       <c r="J17">
         <f t="shared" si="0"/>
-        <v>1555703</v>
+        <v>1705703</v>
       </c>
       <c r="K17">
         <f t="shared" si="2"/>
-        <v>1.1067081737749724</v>
+        <v>1.1558579199202008</v>
       </c>
       <c r="M17">
         <f t="shared" si="3"/>
-        <v>1.121222379332677</v>
+        <v>1.520625705299357</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -2851,33 +2851,33 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>150000</v>
+        <v>260000</v>
       </c>
       <c r="E18">
-        <v>40</v>
+        <v>2000</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18">
         <f t="shared" si="4"/>
-        <v>3130</v>
+        <v>8670</v>
       </c>
       <c r="H18">
         <f t="shared" si="1"/>
-        <v>1.0129449838187703</v>
+        <v>1.2998500749625188</v>
       </c>
       <c r="J18">
         <f t="shared" si="0"/>
-        <v>1705703</v>
+        <v>1965703</v>
       </c>
       <c r="K18">
         <f t="shared" si="2"/>
-        <v>1.0964194322438152</v>
+        <v>1.1524298192592732</v>
       </c>
       <c r="M18">
         <f t="shared" si="3"/>
-        <v>1.1106125640527966</v>
+        <v>1.4979859869532084</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -2891,33 +2891,33 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>2600</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19">
         <f t="shared" si="4"/>
-        <v>3170</v>
+        <v>11270</v>
       </c>
       <c r="H19">
         <f t="shared" si="1"/>
-        <v>1.0127795527156549</v>
+        <v>1.2998846597462514</v>
       </c>
       <c r="J19">
         <f t="shared" si="0"/>
-        <v>1855703</v>
+        <v>2265703</v>
       </c>
       <c r="K19">
         <f t="shared" si="2"/>
-        <v>1.0879402803418883</v>
+        <v>1.1526171552874467</v>
       </c>
       <c r="M19">
         <f t="shared" si="3"/>
-        <v>1.1018436705060017</v>
+        <v>1.498269358718515</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -2931,33 +2931,33 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>600000</v>
+        <v>3000000</v>
       </c>
       <c r="E20">
-        <v>160</v>
+        <v>4000</v>
       </c>
       <c r="F20">
         <v>4</v>
       </c>
       <c r="G20">
         <f t="shared" si="4"/>
-        <v>3330</v>
+        <v>15270</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>1.0504731861198737</v>
+        <v>1.3549245785270629</v>
       </c>
       <c r="J20">
         <f t="shared" si="0"/>
-        <v>2455703</v>
+        <v>5265703</v>
       </c>
       <c r="K20">
         <f t="shared" si="2"/>
-        <v>1.3233276014534654</v>
+        <v>2.324092345731104</v>
       </c>
       <c r="M20">
         <f t="shared" si="3"/>
-        <v>1.3901201617791923</v>
+        <v>3.148969841997689</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -2981,23 +2981,23 @@
       </c>
       <c r="G21">
         <f t="shared" si="4"/>
-        <v>3380</v>
+        <v>15320</v>
       </c>
       <c r="H21">
         <f t="shared" si="1"/>
-        <v>1.015015015015015</v>
+        <v>1.0032743942370661</v>
       </c>
       <c r="J21">
         <f t="shared" si="0"/>
-        <v>2655703</v>
+        <v>5465703</v>
       </c>
       <c r="K21">
         <f t="shared" si="2"/>
-        <v>1.0814430735312861</v>
+        <v>1.037981633221623</v>
       </c>
       <c r="M21">
         <f t="shared" si="3"/>
-        <v>1.0976809575182422</v>
+        <v>1.0413803942996243</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -3021,23 +3021,23 @@
       </c>
       <c r="G22">
         <f t="shared" si="4"/>
-        <v>3430</v>
+        <v>15370</v>
       </c>
       <c r="H22">
         <f t="shared" si="1"/>
-        <v>1.014792899408284</v>
+        <v>1.0032637075718016</v>
       </c>
       <c r="J22">
         <f t="shared" si="0"/>
-        <v>2855703</v>
+        <v>5665703</v>
       </c>
       <c r="K22">
         <f t="shared" si="2"/>
-        <v>1.0753096261140647</v>
+        <v>1.0365918162768815</v>
       </c>
       <c r="M22">
         <f t="shared" si="3"/>
-        <v>1.0912165732459296</v>
+        <v>1.039974948836532</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -3061,23 +3061,23 @@
       </c>
       <c r="G23">
         <f t="shared" si="4"/>
-        <v>3480</v>
+        <v>15420</v>
       </c>
       <c r="H23">
         <f t="shared" si="1"/>
-        <v>1.0145772594752187</v>
+        <v>1.003253090435914</v>
       </c>
       <c r="J23">
         <f t="shared" si="0"/>
-        <v>3055703</v>
+        <v>5865703</v>
       </c>
       <c r="K23">
         <f t="shared" si="2"/>
-        <v>1.0700352942865556</v>
+        <v>1.0353001207440631</v>
       </c>
       <c r="M23">
         <f t="shared" si="3"/>
-        <v>1.0856334764190128</v>
+        <v>1.0386680456651562</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -3101,23 +3101,23 @@
       </c>
       <c r="G24">
         <f t="shared" si="4"/>
-        <v>3530</v>
+        <v>15470</v>
       </c>
       <c r="H24">
         <f t="shared" si="1"/>
-        <v>1.014367816091954</v>
+        <v>1.003242542153048</v>
       </c>
       <c r="J24">
         <f t="shared" si="0"/>
-        <v>3255703</v>
+        <v>6065703</v>
       </c>
       <c r="K24">
         <f t="shared" si="2"/>
-        <v>1.0654513871276103</v>
+        <v>1.0340965098301089</v>
       </c>
       <c r="M24">
         <f t="shared" si="3"/>
-        <v>1.0807595967127772</v>
+        <v>1.0374496113535527</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -3141,23 +3141,23 @@
       </c>
       <c r="G25">
         <f t="shared" si="4"/>
-        <v>3580</v>
+        <v>15520</v>
       </c>
       <c r="H25">
         <f t="shared" si="1"/>
-        <v>1.0141643059490084</v>
+        <v>1.0032320620555915</v>
       </c>
       <c r="J25">
         <f t="shared" si="0"/>
-        <v>3455703</v>
+        <v>6265703</v>
       </c>
       <c r="K25">
         <f t="shared" si="2"/>
-        <v>1.0614306648978731</v>
+        <v>1.0329722704853832</v>
       </c>
       <c r="M25">
         <f t="shared" si="3"/>
-        <v>1.076465093579146</v>
+        <v>1.0363109009652971</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -3181,23 +3181,23 @@
       </c>
       <c r="G26">
         <f t="shared" si="4"/>
-        <v>3780</v>
+        <v>15720</v>
       </c>
       <c r="H26">
         <f t="shared" si="1"/>
-        <v>1.0558659217877095</v>
+        <v>1.0128865979381443</v>
       </c>
       <c r="J26">
         <f t="shared" si="0"/>
-        <v>4455703</v>
+        <v>7265703</v>
       </c>
       <c r="K26">
         <f t="shared" si="2"/>
-        <v>1.2893767201637409</v>
+        <v>1.1595990106776526</v>
       </c>
       <c r="M26">
         <f t="shared" si="3"/>
-        <v>1.3614089391673019</v>
+        <v>1.1745422968977253</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
@@ -3221,23 +3221,23 @@
       </c>
       <c r="G27">
         <f t="shared" si="4"/>
-        <v>3830</v>
+        <v>15770</v>
       </c>
       <c r="H27">
         <f t="shared" si="1"/>
-        <v>1.0132275132275133</v>
+        <v>1.0031806615776082</v>
       </c>
       <c r="J27">
         <f t="shared" si="0"/>
-        <v>4655703</v>
+        <v>7465703</v>
       </c>
       <c r="K27">
         <f t="shared" si="2"/>
-        <v>1.0448862951592599</v>
+        <v>1.0275265862092078</v>
       </c>
       <c r="M27">
         <f t="shared" si="3"/>
-        <v>1.0587075424497263</v>
+        <v>1.0307948005419343</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -3261,23 +3261,23 @@
       </c>
       <c r="G28">
         <f t="shared" si="4"/>
-        <v>3880</v>
+        <v>15820</v>
       </c>
       <c r="H28">
         <f t="shared" si="1"/>
-        <v>1.0130548302872062</v>
+        <v>1.0031705770450221</v>
       </c>
       <c r="J28">
         <f t="shared" si="0"/>
-        <v>4855703</v>
+        <v>7665703</v>
       </c>
       <c r="K28">
         <f t="shared" si="2"/>
-        <v>1.0429580666979832</v>
+        <v>1.026789171763195</v>
       </c>
       <c r="M28">
         <f t="shared" si="3"/>
-        <v>1.056573707255398</v>
+        <v>1.0300446859412646</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -3301,23 +3301,23 @@
       </c>
       <c r="G29">
         <f t="shared" si="4"/>
-        <v>3930</v>
+        <v>15870</v>
       </c>
       <c r="H29">
         <f t="shared" si="1"/>
-        <v>1.0128865979381443</v>
+        <v>1.0031605562579013</v>
       </c>
       <c r="J29">
         <f t="shared" si="0"/>
-        <v>5055703</v>
+        <v>7865703</v>
       </c>
       <c r="K29">
         <f t="shared" si="2"/>
-        <v>1.0411886806091724</v>
+        <v>1.0260902359509623</v>
       </c>
       <c r="M29">
         <f t="shared" si="3"/>
-        <v>1.0546060605139296</v>
+        <v>1.0293332518673686</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -3341,23 +3341,23 @@
       </c>
       <c r="G30">
         <f t="shared" si="4"/>
-        <v>3980</v>
+        <v>15920</v>
       </c>
       <c r="H30">
         <f t="shared" si="1"/>
-        <v>1.0127226463104326</v>
+        <v>1.0031505986137366</v>
       </c>
       <c r="J30">
         <f t="shared" si="0"/>
-        <v>5255703</v>
+        <v>8065703</v>
       </c>
       <c r="K30">
         <f t="shared" si="2"/>
-        <v>1.0395592858203895</v>
+        <v>1.0254268436019005</v>
       </c>
       <c r="M30">
         <f t="shared" si="3"/>
-        <v>1.0527852309326082</v>
+        <v>1.028657551993841</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
@@ -3381,23 +3381,23 @@
       </c>
       <c r="G31">
         <f t="shared" si="4"/>
-        <v>4030</v>
+        <v>15970</v>
       </c>
       <c r="H31">
         <f t="shared" si="1"/>
-        <v>1.0125628140703518</v>
+        <v>1.0031407035175879</v>
       </c>
       <c r="J31">
         <f t="shared" si="0"/>
-        <v>5455703</v>
+        <v>8265703</v>
       </c>
       <c r="K31">
         <f t="shared" si="2"/>
-        <v>1.0380539006865495</v>
+        <v>1.024796350671479</v>
       </c>
       <c r="M31">
         <f t="shared" si="3"/>
-        <v>1.051094778835878</v>
+        <v>1.0280149321748442</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
@@ -3421,23 +3421,23 @@
       </c>
       <c r="G32">
         <f t="shared" si="4"/>
-        <v>4230</v>
+        <v>16170</v>
       </c>
       <c r="H32">
         <f t="shared" si="1"/>
-        <v>1.0496277915632755</v>
+        <v>1.0125234815278648</v>
       </c>
       <c r="J32">
         <f t="shared" si="0"/>
-        <v>6455703</v>
+        <v>9265703</v>
       </c>
       <c r="K32">
         <f t="shared" si="2"/>
-        <v>1.1832944351992767</v>
+        <v>1.1209818451013787</v>
       </c>
       <c r="M32">
         <f t="shared" si="3"/>
-        <v>1.2420187247873302</v>
+        <v>1.1350204405315776</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -3461,23 +3461,23 @@
       </c>
       <c r="G33">
         <f t="shared" si="4"/>
-        <v>4229</v>
+        <v>16169</v>
       </c>
       <c r="H33">
         <f t="shared" si="1"/>
-        <v>0.99976359338061471</v>
+        <v>0.99993815708101419</v>
       </c>
       <c r="J33">
         <f t="shared" si="0"/>
-        <v>6455702</v>
+        <v>9265702</v>
       </c>
       <c r="K33">
         <f t="shared" si="2"/>
-        <v>0.99999984509820228</v>
+        <v>0.99999989207510753</v>
       </c>
       <c r="M33">
         <f t="shared" si="3"/>
-        <v>0.99976343851543681</v>
+        <v>0.99993804916279616</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <f>G2+L1</f>
+        <f t="shared" ref="L2:L38" si="0">G2+L1</f>
         <v>126</v>
       </c>
       <c r="M2" s="12">
@@ -3575,7 +3575,7 @@
         <v>1.26</v>
       </c>
       <c r="N2">
-        <f>N1+D2</f>
+        <f t="shared" ref="N2:N38" si="1">N1+D2</f>
         <v>675000</v>
       </c>
       <c r="O2">
@@ -3622,23 +3622,23 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <f>G3+L2</f>
+        <f t="shared" si="0"/>
         <v>160</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ref="M3:M38" si="0">L3/L2</f>
+        <f t="shared" ref="M3:M38" si="2">L3/L2</f>
         <v>1.2698412698412698</v>
       </c>
       <c r="N3">
-        <f>N2+D3</f>
+        <f t="shared" si="1"/>
         <v>750000</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O38" si="1">N3/N2</f>
+        <f t="shared" ref="O3:O38" si="3">N3/N2</f>
         <v>1.1111111111111112</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q38" si="2">O3*M3</f>
+        <f t="shared" ref="Q3:Q38" si="4">O3*M3</f>
         <v>1.4109347442680775</v>
       </c>
     </row>
@@ -3677,23 +3677,23 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <f>G4+L3</f>
+        <f t="shared" si="0"/>
         <v>202</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2625</v>
       </c>
       <c r="N4">
-        <f>N3+D4</f>
+        <f t="shared" si="1"/>
         <v>825000</v>
       </c>
       <c r="O4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3887500000000002</v>
       </c>
     </row>
@@ -3732,23 +3732,23 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <f>G5+L4</f>
+        <f t="shared" si="0"/>
         <v>255</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2623762376237624</v>
       </c>
       <c r="N5">
-        <f>N4+D5</f>
+        <f t="shared" si="1"/>
         <v>900000</v>
       </c>
       <c r="O5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0909090909090908</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3771377137713769</v>
       </c>
     </row>
@@ -3787,23 +3787,23 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <f>G6+L5</f>
+        <f t="shared" si="0"/>
         <v>322</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2627450980392156</v>
       </c>
       <c r="N6">
-        <f>N5+D6</f>
+        <f t="shared" si="1"/>
         <v>975000</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0833333333333333</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3679738562091501</v>
       </c>
     </row>
@@ -3842,23 +3842,23 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <f>G7+L6</f>
+        <f t="shared" si="0"/>
         <v>652</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.0248447204968945</v>
       </c>
       <c r="N7">
-        <f>N6+D7</f>
+        <f t="shared" si="1"/>
         <v>1275000</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3076923076923077</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.6478738652651699</v>
       </c>
     </row>
@@ -3897,23 +3897,23 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <f>G8+L7</f>
+        <f t="shared" si="0"/>
         <v>822</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2607361963190185</v>
       </c>
       <c r="N8">
-        <f>N7+D8</f>
+        <f t="shared" si="1"/>
         <v>1475000</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1568627450980393</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4584987369180804</v>
       </c>
     </row>
@@ -3952,23 +3952,23 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <f>G9+L8</f>
+        <f t="shared" si="0"/>
         <v>1037</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2615571776155718</v>
       </c>
       <c r="N9">
-        <f>N8+D9</f>
+        <f t="shared" si="1"/>
         <v>1675000</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1355932203389831</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4326157779702258</v>
       </c>
       <c r="W9">
@@ -4010,23 +4010,23 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <f>G10+L9</f>
+        <f t="shared" si="0"/>
         <v>1307</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2603664416586307</v>
       </c>
       <c r="N10">
-        <f>N9+D10</f>
+        <f t="shared" si="1"/>
         <v>1775000</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0597014925373134</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3356121993695935</v>
       </c>
     </row>
@@ -4065,23 +4065,23 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <f>G11+L10</f>
+        <f t="shared" si="0"/>
         <v>1657</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2677888293802602</v>
       </c>
       <c r="N11">
-        <f>N10+D11</f>
+        <f t="shared" si="1"/>
         <v>1875000</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.056338028169014</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3392135521622466</v>
       </c>
     </row>
@@ -4120,23 +4120,23 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <f>G12+L11</f>
+        <f t="shared" si="0"/>
         <v>2087</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2595051297525648</v>
       </c>
       <c r="N12">
-        <f>N11+D12</f>
+        <f t="shared" si="1"/>
         <v>1975000</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0533333333333332</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3266787366727015</v>
       </c>
     </row>
@@ -4175,23 +4175,23 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <f>G13+L12</f>
+        <f t="shared" si="0"/>
         <v>4387</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.1020603737422139</v>
       </c>
       <c r="N13">
-        <f>N12+D13</f>
+        <f t="shared" si="1"/>
         <v>2375000</v>
       </c>
       <c r="O13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2025316455696202</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.5277941203229153</v>
       </c>
     </row>
@@ -4230,23 +4230,23 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <f>G14+L13</f>
+        <f t="shared" si="0"/>
         <v>5537</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2621381354000456</v>
       </c>
       <c r="N14">
-        <f>N13+D14</f>
+        <f t="shared" si="1"/>
         <v>2575000</v>
       </c>
       <c r="O14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0842105263157895</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3684234520653127</v>
       </c>
     </row>
@@ -4285,23 +4285,23 @@
         <v>1</v>
       </c>
       <c r="L15">
-        <f>G15+L14</f>
+        <f t="shared" si="0"/>
         <v>6987</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2618746613689724</v>
       </c>
       <c r="N15">
-        <f>N14+D15</f>
+        <f t="shared" si="1"/>
         <v>2775000</v>
       </c>
       <c r="O15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0776699029126213</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3598843438053974</v>
       </c>
     </row>
@@ -4340,23 +4340,23 @@
         <v>1</v>
       </c>
       <c r="L16">
-        <f>G16+L15</f>
+        <f t="shared" si="0"/>
         <v>8837</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.264777443824245</v>
       </c>
       <c r="N16">
-        <f>N15+D16</f>
+        <f t="shared" si="1"/>
         <v>2975000</v>
       </c>
       <c r="O16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.072072072072072</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.355932574910677</v>
       </c>
     </row>
@@ -4395,23 +4395,23 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <f>G17+L16</f>
+        <f t="shared" si="0"/>
         <v>11137</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2602693221681567</v>
       </c>
       <c r="N17">
-        <f>N16+D17</f>
+        <f t="shared" si="1"/>
         <v>3175000</v>
       </c>
       <c r="O17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0672268907563025</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3449933102130747</v>
       </c>
     </row>
@@ -4450,23 +4450,23 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <f>G18+L17</f>
+        <f t="shared" si="0"/>
         <v>14037</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2603932836490976</v>
       </c>
       <c r="N18">
-        <f>N17+D18</f>
+        <f t="shared" si="1"/>
         <v>3375000</v>
       </c>
       <c r="O18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0629921259842521</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3397881361624269</v>
       </c>
     </row>
@@ -4505,23 +4505,23 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <f>G19+L18</f>
+        <f t="shared" si="0"/>
         <v>29037</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.0686044026501391</v>
       </c>
       <c r="N19">
-        <f>N18+D19</f>
+        <f t="shared" si="1"/>
         <v>3975000</v>
       </c>
       <c r="O19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1777777777777778</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.4363562964546084</v>
       </c>
     </row>
@@ -4560,24 +4560,24 @@
         <v>1</v>
       </c>
       <c r="L20" s="1">
-        <f>G20+L19</f>
+        <f t="shared" si="0"/>
         <v>36637</v>
       </c>
       <c r="M20" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2617350277232497</v>
       </c>
       <c r="N20" s="1">
-        <f>N19+D20</f>
+        <f t="shared" si="1"/>
         <v>4215000</v>
       </c>
       <c r="O20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.060377358490566</v>
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3379152558122007</v>
       </c>
     </row>
@@ -4616,23 +4616,23 @@
         <v>1</v>
       </c>
       <c r="L21">
-        <f>G21+L20</f>
+        <f t="shared" si="0"/>
         <v>46337</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2647596691868876</v>
       </c>
       <c r="N21">
-        <f>N20+D21</f>
+        <f t="shared" si="1"/>
         <v>4455000</v>
       </c>
       <c r="O21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0569395017793595</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3367744546210165</v>
       </c>
     </row>
@@ -4671,23 +4671,23 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <f>G22+L21</f>
+        <f t="shared" si="0"/>
         <v>58337</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2589723115436908</v>
       </c>
       <c r="N22">
-        <f>N21+D22</f>
+        <f t="shared" si="1"/>
         <v>4695000</v>
       </c>
       <c r="O22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0538720538720538</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3267957357345967</v>
       </c>
     </row>
@@ -4726,23 +4726,23 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <f>G23+L22</f>
+        <f t="shared" si="0"/>
         <v>73837</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2656975847232459</v>
       </c>
       <c r="N23">
-        <f>N22+D23</f>
+        <f t="shared" si="1"/>
         <v>4935000</v>
       </c>
       <c r="O23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0511182108626198</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3303977807474374</v>
       </c>
     </row>
@@ -4781,23 +4781,23 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <f>G24+L23</f>
+        <f t="shared" si="0"/>
         <v>92837</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2573235640667957</v>
       </c>
       <c r="N24">
-        <f>N23+D24</f>
+        <f t="shared" si="1"/>
         <v>5175000</v>
       </c>
       <c r="O24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0486322188449848</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3184699987934483</v>
       </c>
     </row>
@@ -4836,24 +4836,24 @@
         <v>5</v>
       </c>
       <c r="L25" s="1">
-        <f>G25+L24</f>
+        <f t="shared" si="0"/>
         <v>192837</v>
       </c>
       <c r="M25" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.077156737076812</v>
       </c>
       <c r="N25" s="1">
-        <f>N24+D25</f>
+        <f t="shared" si="1"/>
         <v>6175000</v>
       </c>
       <c r="O25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1932367149758454</v>
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.4785396814394809</v>
       </c>
     </row>
@@ -4892,23 +4892,23 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <f>G26+L25</f>
+        <f t="shared" si="0"/>
         <v>242837</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2592863402770216</v>
       </c>
       <c r="N26">
-        <f>N25+D26</f>
+        <f t="shared" si="1"/>
         <v>6475000</v>
       </c>
       <c r="O26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.048582995951417</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3204662434483749</v>
       </c>
     </row>
@@ -4947,23 +4947,23 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <f>G27+L26</f>
+        <f t="shared" si="0"/>
         <v>307837</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.267669259626828</v>
       </c>
       <c r="N27">
-        <f>N26+D27</f>
+        <f t="shared" si="1"/>
         <v>6775000</v>
       </c>
       <c r="O27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0463320463320462</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3264029704975688</v>
       </c>
     </row>
@@ -5002,23 +5002,23 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <f>G28+L27</f>
+        <f t="shared" si="0"/>
         <v>387837</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.259877792468092</v>
       </c>
       <c r="N28">
-        <f>N27+D28</f>
+        <f t="shared" si="1"/>
         <v>7075000</v>
       </c>
       <c r="O28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0442804428044281</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3156657389980444</v>
       </c>
     </row>
@@ -5057,23 +5057,23 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <f>G29+L28</f>
+        <f t="shared" si="0"/>
         <v>487837</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2578402782612284</v>
       </c>
       <c r="N29">
-        <f>N28+D29</f>
+        <f t="shared" si="1"/>
         <v>7375000</v>
       </c>
       <c r="O29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0424028268551238</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.31117626179174</v>
       </c>
     </row>
@@ -5112,23 +5112,23 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <f>G30+L29</f>
+        <f t="shared" si="0"/>
         <v>617837</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2664824521305271</v>
       </c>
       <c r="N30">
-        <f>N29+D30</f>
+        <f t="shared" si="1"/>
         <v>7675000</v>
       </c>
       <c r="O30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0406779661016949</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3180003823866842</v>
       </c>
     </row>
@@ -5167,23 +5167,23 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <f>G31+L30</f>
+        <f t="shared" si="0"/>
         <v>777837</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.2589679802277947</v>
       </c>
       <c r="N31">
-        <f>N30+D31</f>
+        <f t="shared" si="1"/>
         <v>9875000</v>
       </c>
       <c r="O31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2866449511400651</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6198447954070971</v>
       </c>
     </row>
@@ -5222,23 +5222,23 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <f>G32+L31</f>
+        <f t="shared" si="0"/>
         <v>977837</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.257123279041753</v>
       </c>
       <c r="N32">
-        <f>N31+D32</f>
+        <f t="shared" si="1"/>
         <v>10275000</v>
       </c>
       <c r="O32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.040506329113924</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3080447283193937</v>
       </c>
     </row>
@@ -5277,23 +5277,23 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <f>G33+L32</f>
+        <f t="shared" si="0"/>
         <v>994837</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.0173853106397079</v>
       </c>
       <c r="N33">
-        <f>N32+D33</f>
+        <f t="shared" si="1"/>
         <v>10675000</v>
       </c>
       <c r="O33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0389294403892944</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0569915514432002</v>
       </c>
     </row>
@@ -5332,23 +5332,23 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <f>G34+L33</f>
+        <f t="shared" si="0"/>
         <v>1014837</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.0201037958982224</v>
       </c>
       <c r="N34">
-        <f>N33+D34</f>
+        <f t="shared" si="1"/>
         <v>11075000</v>
       </c>
       <c r="O34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0374707259953162</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0583278257211066</v>
       </c>
     </row>
@@ -5387,23 +5387,23 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <f>G35+L34</f>
+        <f t="shared" si="0"/>
         <v>1037837</v>
       </c>
       <c r="M35" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.0226637381175498</v>
       </c>
       <c r="N35">
-        <f>N34+D35</f>
+        <f t="shared" si="1"/>
         <v>11475000</v>
       </c>
       <c r="O35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0361173814898419</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0595996744829692</v>
       </c>
     </row>
@@ -5442,23 +5442,23 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <f>G36+L35</f>
+        <f t="shared" si="0"/>
         <v>1064837</v>
       </c>
       <c r="M36" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.0260156460022143</v>
       </c>
       <c r="N36">
-        <f>N35+D36</f>
+        <f t="shared" si="1"/>
         <v>11875000</v>
       </c>
       <c r="O36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0348583877995643</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.06178089727898</v>
       </c>
     </row>
@@ -5497,23 +5497,23 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <f>G37+L36</f>
+        <f t="shared" si="0"/>
         <v>1164837</v>
       </c>
       <c r="M37" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.0939110868611817</v>
       </c>
       <c r="N37">
-        <f>N36+D37</f>
+        <f t="shared" si="1"/>
         <v>16375000</v>
       </c>
       <c r="O37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3789473684210527</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.50844581451384</v>
       </c>
     </row>
@@ -5552,23 +5552,23 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <f>G38+L37</f>
+        <f t="shared" si="0"/>
         <v>1164836</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.9999991415107865</v>
       </c>
       <c r="N38">
-        <f>N37+D38</f>
+        <f t="shared" si="1"/>
         <v>16374999</v>
       </c>
       <c r="O38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99999993893129768</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.99999908044213659</v>
       </c>
     </row>
@@ -5612,6 +5612,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F73C74-20E1-4CF2-8AE1-F98B6BF5F0A1}">
   <dimension ref="A1:X68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="13.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -6056,8 +6059,8 @@
         <v>251751106392</v>
       </c>
       <c r="E11">
-        <f>5000/2*(C6+(1000)*E6)</f>
-        <v>2629377765980000</v>
+        <f>1000/2*(2*C6+(1000)*E6)</f>
+        <v>651751106392000</v>
       </c>
       <c r="H11">
         <v>125</v>
@@ -6072,8 +6075,8 @@
         <v>108986538392</v>
       </c>
       <c r="E12">
-        <f>5000/2*(C7+(5000)*E7)</f>
-        <v>5522466345980000</v>
+        <f>5000/2*(2*C7+(5000)*E7)</f>
+        <v>5794932691960000</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">

--- a/정기/BM/각성 절멸타 수치/각성 절멸타 수치.xlsx
+++ b/정기/BM/각성 절멸타 수치/각성 절멸타 수치.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\BM\각성 절멸타 수치\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694A4C8D-B188-442A-80BD-7E7DE9A575FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44DFDE6-AD02-4565-A416-30D7432D8076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15495" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{3E321328-0C01-4213-932A-34E838058470}"/>
+    <workbookView xWindow="6660" yWindow="465" windowWidth="19200" windowHeight="15480" xr2:uid="{3E321328-0C01-4213-932A-34E838058470}"/>
   </bookViews>
   <sheets>
     <sheet name="보스체력" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="122">
   <si>
     <t>아이디</t>
   </si>
@@ -460,6 +460,10 @@
   </si>
   <si>
     <t>수정 각성 보유 예정 수치1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -932,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8741954B-DBD0-4949-91DB-6228BE175F92}">
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1243,7 +1247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1260,7 +1264,7 @@
         <v>3.4145488738336023</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1277,7 +1281,7 @@
         <v>3.6869450645195756</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1294,7 +1298,7 @@
         <v>3.9810717055349727</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1311,7 +1315,7 @@
         <v>4.2986623470822769</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1323,8 +1327,11 @@
         <f t="shared" si="2"/>
         <v>1.0797751623277099</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <v>41250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1336,8 +1343,15 @@
         <f t="shared" si="2"/>
         <v>1.0797751623277094</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <f>I21*4</f>
+        <v>165000</v>
+      </c>
+      <c r="J22">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1349,8 +1363,12 @@
         <f t="shared" si="2"/>
         <v>1.0797751623277096</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f>I22/11*20</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1363,7 +1381,7 @@
         <v>1.0797751623277101</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1376,7 +1394,7 @@
         <v>1.0797751623277096</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1388,8 +1406,19 @@
         <f t="shared" si="2"/>
         <v>1.0797751623277094</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <v>330000</v>
+      </c>
+      <c r="J26">
+        <f>I26/6*2</f>
+        <v>110000</v>
+      </c>
+      <c r="K26">
+        <f>J26/2.5</f>
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1402,7 +1431,7 @@
         <v>1.0797751623277099</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1415,7 +1444,7 @@
         <v>1.0797751623277096</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1428,7 +1457,7 @@
         <v>1.0797751623277092</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1441,7 +1470,7 @@
         <v>1.0797751623277101</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1454,7 +1483,7 @@
         <v>1.0797751623277092</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2190,10 +2219,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22727E31-19EA-48A7-B6B9-1C0D6FA6B8D4}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -2204,7 +2236,7 @@
         <v>6203</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2234,8 +2266,11 @@
         <f>J3/J2</f>
         <v>1.1712952058754256</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O2">
+        <v>46703</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2274,8 +2309,17 @@
         <f>K3*H3</f>
         <v>1.5226837676380534</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O3">
+        <v>8000</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2314,8 +2358,17 @@
         <f t="shared" ref="M4:M33" si="3">K4*H4</f>
         <v>1.5228401198640491</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O4">
+        <v>9000</v>
+      </c>
+      <c r="P4">
+        <v>40</v>
+      </c>
+      <c r="Q4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2354,8 +2407,17 @@
         <f t="shared" si="3"/>
         <v>1.5175811278626641</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O5">
+        <v>11000</v>
+      </c>
+      <c r="P5">
+        <v>50</v>
+      </c>
+      <c r="Q5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2394,8 +2456,17 @@
         <f t="shared" si="3"/>
         <v>1.5282847348226247</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O6">
+        <v>15000</v>
+      </c>
+      <c r="P6">
+        <v>60</v>
+      </c>
+      <c r="Q6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2434,8 +2505,17 @@
         <f t="shared" si="3"/>
         <v>1.5286974794599959</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O7">
+        <v>20000</v>
+      </c>
+      <c r="P7">
+        <v>70</v>
+      </c>
+      <c r="Q7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2474,12 +2554,21 @@
         <f t="shared" si="2"/>
         <v>2.2305953346763534</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <f t="shared" si="3"/>
         <v>3.3777586496527636</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O8" s="1">
+        <v>135000</v>
+      </c>
+      <c r="P8" s="1">
+        <v>180</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2518,8 +2607,17 @@
         <f t="shared" si="3"/>
         <v>1.5040571708838568</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O9">
+        <v>38000</v>
+      </c>
+      <c r="P9">
+        <v>160</v>
+      </c>
+      <c r="Q9">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2558,8 +2656,17 @@
         <f t="shared" si="3"/>
         <v>1.5027431615511686</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O10">
+        <v>43000</v>
+      </c>
+      <c r="P10">
+        <v>210</v>
+      </c>
+      <c r="Q10">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2598,8 +2705,17 @@
         <f t="shared" si="3"/>
         <v>1.4995683183759438</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O11">
+        <v>50000</v>
+      </c>
+      <c r="P11">
+        <v>270</v>
+      </c>
+      <c r="Q11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2638,8 +2754,17 @@
         <f t="shared" si="3"/>
         <v>1.5066196018490785</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O12">
+        <v>60000</v>
+      </c>
+      <c r="P12">
+        <v>350</v>
+      </c>
+      <c r="Q12">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2678,8 +2803,17 @@
         <f t="shared" si="3"/>
         <v>1.5042763165444544</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O13">
+        <v>70000</v>
+      </c>
+      <c r="P13">
+        <v>450</v>
+      </c>
+      <c r="Q13">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -2715,12 +2849,21 @@
         <f t="shared" si="2"/>
         <v>2.1864671556229647</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <f t="shared" si="3"/>
         <v>3.2963489605077183</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O14" s="1">
+        <v>600000</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2734,18 +2877,18 @@
         <v>170000</v>
       </c>
       <c r="E15">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
         <f t="shared" si="4"/>
-        <v>3870</v>
+        <v>3970</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>1.303030303030303</v>
+        <v>1.3367003367003367</v>
       </c>
       <c r="J15">
         <f t="shared" si="0"/>
@@ -2757,10 +2900,20 @@
       </c>
       <c r="M15">
         <f t="shared" si="3"/>
-        <v>1.5033690481681488</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5422157935988503</v>
+      </c>
+      <c r="O15">
+        <f>SUM(O2:O14)</f>
+        <v>1105703</v>
+      </c>
+      <c r="P15">
+        <v>1000</v>
+      </c>
+      <c r="Q15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2774,18 +2927,18 @@
         <v>200000</v>
       </c>
       <c r="E16">
-        <v>1200</v>
+        <v>1330</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
         <f t="shared" si="4"/>
-        <v>5070</v>
+        <v>5300</v>
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>1.3100775193798451</v>
+        <v>1.3350125944584383</v>
       </c>
       <c r="J16">
         <f t="shared" si="0"/>
@@ -2797,10 +2950,16 @@
       </c>
       <c r="M16">
         <f t="shared" si="3"/>
-        <v>1.5154666294438404</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5443109334069927</v>
+      </c>
+      <c r="P16">
+        <v>1330</v>
+      </c>
+      <c r="Q16">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2814,18 +2973,18 @@
         <v>230000</v>
       </c>
       <c r="E17">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17">
         <f t="shared" si="4"/>
-        <v>6670</v>
+        <v>7000</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>1.3155818540433926</v>
+        <v>1.320754716981132</v>
       </c>
       <c r="J17">
         <f t="shared" si="0"/>
@@ -2837,10 +2996,16 @@
       </c>
       <c r="M17">
         <f t="shared" si="3"/>
-        <v>1.520625705299357</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5266047998946048</v>
+      </c>
+      <c r="P17">
+        <v>1700</v>
+      </c>
+      <c r="Q17">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2854,18 +3019,18 @@
         <v>260000</v>
       </c>
       <c r="E18">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18">
         <f t="shared" si="4"/>
-        <v>8670</v>
+        <v>9200</v>
       </c>
       <c r="H18">
         <f t="shared" si="1"/>
-        <v>1.2998500749625188</v>
+        <v>1.3142857142857143</v>
       </c>
       <c r="J18">
         <f t="shared" si="0"/>
@@ -2877,10 +3042,16 @@
       </c>
       <c r="M18">
         <f t="shared" si="3"/>
-        <v>1.4979859869532084</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5146220481693304</v>
+      </c>
+      <c r="P18">
+        <v>2200</v>
+      </c>
+      <c r="Q18">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2894,18 +3065,18 @@
         <v>300000</v>
       </c>
       <c r="E19">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19">
         <f t="shared" si="4"/>
-        <v>11270</v>
+        <v>12000</v>
       </c>
       <c r="H19">
         <f t="shared" si="1"/>
-        <v>1.2998846597462514</v>
+        <v>1.3043478260869565</v>
       </c>
       <c r="J19">
         <f t="shared" si="0"/>
@@ -2917,50 +3088,64 @@
       </c>
       <c r="M19">
         <f t="shared" si="3"/>
-        <v>1.498269358718515</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20">
+        <v>1.5034136808097132</v>
+      </c>
+      <c r="P19">
+        <v>2800</v>
+      </c>
+      <c r="Q19">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D20">
-        <v>3000000</v>
-      </c>
-      <c r="E20">
-        <v>4000</v>
-      </c>
-      <c r="F20">
+      <c r="D20" s="1">
+        <v>2500000</v>
+      </c>
+      <c r="E20" s="1">
+        <v>6800</v>
+      </c>
+      <c r="F20" s="1">
         <v>4</v>
       </c>
-      <c r="G20">
-        <f t="shared" si="4"/>
-        <v>15270</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
-        <v>1.3549245785270629</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="0"/>
-        <v>5265703</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="2"/>
-        <v>2.324092345731104</v>
-      </c>
-      <c r="M20">
+      <c r="G20" s="1">
+        <f t="shared" si="4"/>
+        <v>18800</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="1"/>
+        <v>1.5666666666666667</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1">
+        <f t="shared" si="0"/>
+        <v>4765703</v>
+      </c>
+      <c r="K20" s="1">
+        <f t="shared" si="2"/>
+        <v>2.1034102881092536</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1">
         <f t="shared" si="3"/>
-        <v>3.148969841997689</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+        <v>3.2953427847044972</v>
+      </c>
+      <c r="P20" s="1">
+        <v>6800</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2971,21 +3156,21 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>200000</v>
+        <v>700000</v>
       </c>
       <c r="E21">
-        <v>50</v>
+        <v>6300</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21">
         <f t="shared" si="4"/>
-        <v>15320</v>
+        <v>25100</v>
       </c>
       <c r="H21">
         <f t="shared" si="1"/>
-        <v>1.0032743942370661</v>
+        <v>1.3351063829787233</v>
       </c>
       <c r="J21">
         <f t="shared" si="0"/>
@@ -2993,14 +3178,21 @@
       </c>
       <c r="K21">
         <f t="shared" si="2"/>
-        <v>1.037981633221623</v>
+        <v>1.1468828418388641</v>
       </c>
       <c r="M21">
         <f t="shared" si="3"/>
-        <v>1.0413803942996243</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5312106026678451</v>
+      </c>
+      <c r="P21">
+        <v>6300</v>
+      </c>
+      <c r="Q21">
+        <f>SUM(Q3:Q20)</f>
+        <v>18700</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3011,36 +3203,39 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>200000</v>
+        <v>800000</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>8500</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22">
         <f t="shared" si="4"/>
-        <v>15370</v>
+        <v>33600</v>
       </c>
       <c r="H22">
         <f t="shared" si="1"/>
-        <v>1.0032637075718016</v>
+        <v>1.3386454183266931</v>
       </c>
       <c r="J22">
         <f t="shared" si="0"/>
-        <v>5665703</v>
+        <v>6265703</v>
       </c>
       <c r="K22">
         <f t="shared" si="2"/>
-        <v>1.0365918162768815</v>
+        <v>1.1463672651075261</v>
       </c>
       <c r="M22">
         <f t="shared" si="3"/>
-        <v>1.039974948836532</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5345792871558914</v>
+      </c>
+      <c r="P22">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3051,36 +3246,39 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>200000</v>
+        <v>900000</v>
       </c>
       <c r="E23">
-        <v>50</v>
+        <v>11000</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23">
         <f t="shared" si="4"/>
-        <v>15420</v>
+        <v>44600</v>
       </c>
       <c r="H23">
         <f t="shared" si="1"/>
-        <v>1.003253090435914</v>
+        <v>1.3273809523809523</v>
       </c>
       <c r="J23">
         <f t="shared" si="0"/>
-        <v>5865703</v>
+        <v>7165703</v>
       </c>
       <c r="K23">
         <f t="shared" si="2"/>
-        <v>1.0353001207440631</v>
+        <v>1.1436391096098875</v>
       </c>
       <c r="M23">
         <f t="shared" si="3"/>
-        <v>1.0386680456651562</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5180447704940767</v>
+      </c>
+      <c r="P23">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3091,36 +3289,39 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="E24">
-        <v>50</v>
+        <v>15500</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24">
         <f t="shared" si="4"/>
-        <v>15470</v>
+        <v>60100</v>
       </c>
       <c r="H24">
         <f t="shared" si="1"/>
-        <v>1.003242542153048</v>
+        <v>1.3475336322869955</v>
       </c>
       <c r="J24">
         <f t="shared" si="0"/>
-        <v>6065703</v>
+        <v>8165703</v>
       </c>
       <c r="K24">
         <f t="shared" si="2"/>
-        <v>1.0340965098301089</v>
+        <v>1.1395536488185458</v>
       </c>
       <c r="M24">
         <f t="shared" si="3"/>
-        <v>1.0374496113535527</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5355868675783544</v>
+      </c>
+      <c r="P24">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3131,76 +3332,85 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>200000</v>
+        <v>1100000</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>20000</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
         <f t="shared" si="4"/>
-        <v>15520</v>
+        <v>80100</v>
       </c>
       <c r="H25">
         <f t="shared" si="1"/>
-        <v>1.0032320620555915</v>
+        <v>1.3327787021630615</v>
       </c>
       <c r="J25">
         <f t="shared" si="0"/>
-        <v>6265703</v>
+        <v>9265703</v>
       </c>
       <c r="K25">
         <f t="shared" si="2"/>
-        <v>1.0329722704853832</v>
+        <v>1.1347097733042704</v>
       </c>
       <c r="M25">
         <f t="shared" si="3"/>
-        <v>1.0363109009652971</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26">
+        <v>1.5123170189962072</v>
+      </c>
+      <c r="P25">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D26">
-        <v>1000000</v>
-      </c>
-      <c r="E26">
-        <v>200</v>
-      </c>
-      <c r="F26">
+      <c r="D26" s="1">
+        <v>8500000</v>
+      </c>
+      <c r="E26" s="1">
+        <v>60000</v>
+      </c>
+      <c r="F26" s="1">
         <v>4</v>
       </c>
-      <c r="G26">
-        <f t="shared" si="4"/>
-        <v>15720</v>
-      </c>
-      <c r="H26">
-        <f t="shared" si="1"/>
-        <v>1.0128865979381443</v>
-      </c>
-      <c r="J26">
-        <f t="shared" si="0"/>
-        <v>7265703</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="2"/>
-        <v>1.1595990106776526</v>
-      </c>
-      <c r="M26">
+      <c r="G26" s="1">
+        <f t="shared" si="4"/>
+        <v>140100</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="1"/>
+        <v>1.7490636704119851</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1">
+        <f t="shared" si="0"/>
+        <v>17765703</v>
+      </c>
+      <c r="K26" s="1">
+        <f t="shared" si="2"/>
+        <v>1.9173615860555859</v>
+      </c>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1">
         <f t="shared" si="3"/>
-        <v>1.1745422968977253</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+        <v>3.3535874932133285</v>
+      </c>
+      <c r="P26">
+        <f>SUM(P3:P25)</f>
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3211,36 +3421,36 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27">
         <f t="shared" si="4"/>
-        <v>15770</v>
+        <v>190100</v>
       </c>
       <c r="H27">
         <f t="shared" si="1"/>
-        <v>1.0031806615776082</v>
+        <v>1.3568879371877232</v>
       </c>
       <c r="J27">
         <f t="shared" si="0"/>
-        <v>7465703</v>
+        <v>19765703</v>
       </c>
       <c r="K27">
         <f t="shared" si="2"/>
-        <v>1.0275265862092078</v>
+        <v>1.112576462637026</v>
       </c>
       <c r="M27">
         <f t="shared" si="3"/>
-        <v>1.0307948005419343</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5096415813511681</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3251,36 +3461,36 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="E28">
-        <v>50</v>
+        <v>65000</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
         <f t="shared" si="4"/>
-        <v>15820</v>
+        <v>255100</v>
       </c>
       <c r="H28">
         <f t="shared" si="1"/>
-        <v>1.0031705770450221</v>
+        <v>1.341925302472383</v>
       </c>
       <c r="J28">
         <f t="shared" si="0"/>
-        <v>7665703</v>
+        <v>22765703</v>
       </c>
       <c r="K28">
         <f t="shared" si="2"/>
-        <v>1.026789171763195</v>
+        <v>1.151778057173074</v>
       </c>
       <c r="M28">
         <f t="shared" si="3"/>
-        <v>1.0300446859412646</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.545600117753031</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3291,36 +3501,36 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>200000</v>
+        <v>4000000</v>
       </c>
       <c r="E29">
-        <v>50</v>
+        <v>90000</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29">
         <f t="shared" si="4"/>
-        <v>15870</v>
+        <v>345100</v>
       </c>
       <c r="H29">
         <f t="shared" si="1"/>
-        <v>1.0031605562579013</v>
+        <v>1.3528028224225794</v>
       </c>
       <c r="J29">
         <f t="shared" si="0"/>
-        <v>7865703</v>
+        <v>26765703</v>
       </c>
       <c r="K29">
         <f t="shared" si="2"/>
-        <v>1.0260902359509623</v>
+        <v>1.1757028983466928</v>
       </c>
       <c r="M29">
         <f t="shared" si="3"/>
-        <v>1.0293332518673686</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5904941992138131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3331,36 +3541,36 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>200000</v>
+        <v>5000000</v>
       </c>
       <c r="E30">
-        <v>50</v>
+        <v>120000</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30">
         <f t="shared" si="4"/>
-        <v>15920</v>
+        <v>465100</v>
       </c>
       <c r="H30">
         <f t="shared" si="1"/>
-        <v>1.0031505986137366</v>
+        <v>1.3477252970153579</v>
       </c>
       <c r="J30">
         <f t="shared" si="0"/>
-        <v>8065703</v>
+        <v>31765703</v>
       </c>
       <c r="K30">
         <f t="shared" si="2"/>
-        <v>1.0254268436019005</v>
+        <v>1.1868062273574507</v>
       </c>
       <c r="M30">
         <f t="shared" si="3"/>
-        <v>1.028657551993841</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.5994887752649967</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3371,36 +3581,36 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>200000</v>
+        <v>7000000</v>
       </c>
       <c r="E31">
-        <v>50</v>
+        <v>150000</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31">
         <f t="shared" si="4"/>
-        <v>15970</v>
+        <v>615100</v>
       </c>
       <c r="H31">
         <f t="shared" si="1"/>
-        <v>1.0031407035175879</v>
+        <v>1.3225112878950764</v>
       </c>
       <c r="J31">
         <f t="shared" si="0"/>
-        <v>8265703</v>
+        <v>38765703</v>
       </c>
       <c r="K31">
         <f t="shared" si="2"/>
-        <v>1.024796350671479</v>
+        <v>1.2203634529983485</v>
       </c>
       <c r="M31">
         <f t="shared" si="3"/>
-        <v>1.0280149321748442</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1.6139444419249285</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3411,33 +3621,33 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>1000000</v>
+        <v>30000000</v>
       </c>
       <c r="E32">
-        <v>200</v>
+        <v>600000</v>
       </c>
       <c r="F32">
         <v>4</v>
       </c>
       <c r="G32">
         <f t="shared" si="4"/>
-        <v>16170</v>
+        <v>1215100</v>
       </c>
       <c r="H32">
         <f t="shared" si="1"/>
-        <v>1.0125234815278648</v>
+        <v>1.9754511461550968</v>
       </c>
       <c r="J32">
         <f t="shared" si="0"/>
-        <v>9265703</v>
+        <v>68765703</v>
       </c>
       <c r="K32">
         <f t="shared" si="2"/>
-        <v>1.1209818451013787</v>
+        <v>1.7738799422778428</v>
       </c>
       <c r="M32">
         <f t="shared" si="3"/>
-        <v>1.1350204405315776</v>
+        <v>3.5042131651143014</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -3461,23 +3671,23 @@
       </c>
       <c r="G33">
         <f t="shared" si="4"/>
-        <v>16169</v>
+        <v>1215099</v>
       </c>
       <c r="H33">
         <f t="shared" si="1"/>
-        <v>0.99993815708101419</v>
+        <v>0.99999917702246732</v>
       </c>
       <c r="J33">
         <f t="shared" si="0"/>
-        <v>9265702</v>
+        <v>68765702</v>
       </c>
       <c r="K33">
         <f t="shared" si="2"/>
-        <v>0.99999989207510753</v>
+        <v>0.99999998545786695</v>
       </c>
       <c r="M33">
         <f t="shared" si="3"/>
-        <v>0.99993804916279616</v>
+        <v>0.99999916248034626</v>
       </c>
     </row>
   </sheetData>
@@ -3490,6 +3700,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8142A7-5168-4122-94BE-0FC79D3B86C1}">
   <dimension ref="A1:W44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3567,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L38" si="0">G2+L1</f>
+        <f>G2+L1</f>
         <v>126</v>
       </c>
       <c r="M2" s="12">
@@ -3575,7 +3788,7 @@
         <v>1.26</v>
       </c>
       <c r="N2">
-        <f t="shared" ref="N2:N38" si="1">N1+D2</f>
+        <f>N1+D2</f>
         <v>675000</v>
       </c>
       <c r="O2">
@@ -3622,23 +3835,23 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <f t="shared" si="0"/>
+        <f>G3+L2</f>
         <v>160</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ref="M3:M38" si="2">L3/L2</f>
+        <f t="shared" ref="M3:M38" si="0">L3/L2</f>
         <v>1.2698412698412698</v>
       </c>
       <c r="N3">
-        <f t="shared" si="1"/>
+        <f>N2+D3</f>
         <v>750000</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O38" si="3">N3/N2</f>
+        <f t="shared" ref="O3:O38" si="1">N3/N2</f>
         <v>1.1111111111111112</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q38" si="4">O3*M3</f>
+        <f t="shared" ref="Q3:Q38" si="2">O3*M3</f>
         <v>1.4109347442680775</v>
       </c>
     </row>
@@ -3677,23 +3890,23 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <f t="shared" si="0"/>
+        <f>G4+L3</f>
         <v>202</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2625</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
+        <f>N3+D4</f>
         <v>825000</v>
       </c>
       <c r="O4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3887500000000002</v>
       </c>
     </row>
@@ -3732,23 +3945,23 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <f t="shared" si="0"/>
+        <f>G5+L4</f>
         <v>255</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2623762376237624</v>
       </c>
       <c r="N5">
-        <f t="shared" si="1"/>
+        <f>N4+D5</f>
         <v>900000</v>
       </c>
       <c r="O5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0909090909090908</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3771377137713769</v>
       </c>
     </row>
@@ -3787,23 +4000,23 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
+        <f>G6+L5</f>
         <v>322</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2627450980392156</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
+        <f>N5+D6</f>
         <v>975000</v>
       </c>
       <c r="O6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0833333333333333</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3679738562091501</v>
       </c>
     </row>
@@ -3842,23 +4055,23 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <f t="shared" si="0"/>
+        <f>G7+L6</f>
         <v>652</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.0248447204968945</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
+        <f>N6+D7</f>
         <v>1275000</v>
       </c>
       <c r="O7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3076923076923077</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2.6478738652651699</v>
       </c>
     </row>
@@ -3897,23 +4110,23 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
+        <f>G8+L7</f>
         <v>822</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2607361963190185</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
+        <f>N7+D8</f>
         <v>1475000</v>
       </c>
       <c r="O8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.1568627450980393</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.4584987369180804</v>
       </c>
     </row>
@@ -3952,23 +4165,23 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <f t="shared" si="0"/>
+        <f>G9+L8</f>
         <v>1037</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2615571776155718</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f>N8+D9</f>
         <v>1675000</v>
       </c>
       <c r="O9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.1355932203389831</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.4326157779702258</v>
       </c>
       <c r="W9">
@@ -4010,23 +4223,23 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
+        <f>G10+L9</f>
         <v>1307</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2603664416586307</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
+        <f>N9+D10</f>
         <v>1775000</v>
       </c>
       <c r="O10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0597014925373134</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3356121993695935</v>
       </c>
     </row>
@@ -4065,23 +4278,23 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
+        <f>G11+L10</f>
         <v>1657</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2677888293802602</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f>N10+D11</f>
         <v>1875000</v>
       </c>
       <c r="O11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.056338028169014</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3392135521622466</v>
       </c>
     </row>
@@ -4120,23 +4333,23 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <f t="shared" si="0"/>
+        <f>G12+L11</f>
         <v>2087</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2595051297525648</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
+        <f>N11+D12</f>
         <v>1975000</v>
       </c>
       <c r="O12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0533333333333332</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3266787366727015</v>
       </c>
     </row>
@@ -4175,23 +4388,23 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <f t="shared" si="0"/>
+        <f>G13+L12</f>
         <v>4387</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.1020603737422139</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
+        <f>N12+D13</f>
         <v>2375000</v>
       </c>
       <c r="O13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2025316455696202</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2.5277941203229153</v>
       </c>
     </row>
@@ -4214,7 +4427,7 @@
       <c r="F14">
         <v>510000</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14">
         <v>1150</v>
       </c>
       <c r="H14">
@@ -4230,23 +4443,23 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
+        <f>G14+L13</f>
         <v>5537</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2621381354000456</v>
       </c>
       <c r="N14">
-        <f t="shared" si="1"/>
+        <f>N13+D14</f>
         <v>2575000</v>
       </c>
       <c r="O14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0842105263157895</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3684234520653127</v>
       </c>
     </row>
@@ -4285,23 +4498,23 @@
         <v>1</v>
       </c>
       <c r="L15">
-        <f t="shared" si="0"/>
+        <f>G15+L14</f>
         <v>6987</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2618746613689724</v>
       </c>
       <c r="N15">
-        <f t="shared" si="1"/>
+        <f>N14+D15</f>
         <v>2775000</v>
       </c>
       <c r="O15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0776699029126213</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3598843438053974</v>
       </c>
     </row>
@@ -4340,23 +4553,23 @@
         <v>1</v>
       </c>
       <c r="L16">
-        <f t="shared" si="0"/>
+        <f>G16+L15</f>
         <v>8837</v>
       </c>
       <c r="M16" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.264777443824245</v>
       </c>
       <c r="N16">
-        <f t="shared" si="1"/>
+        <f>N15+D16</f>
         <v>2975000</v>
       </c>
       <c r="O16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.072072072072072</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.355932574910677</v>
       </c>
     </row>
@@ -4395,23 +4608,23 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <f t="shared" si="0"/>
+        <f>G17+L16</f>
         <v>11137</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.2602693221681567</v>
       </c>
       <c r="N17">
-        <f t="shared" si="1"/>
+        <f>N16+D17</f>
         <v>3175000</v>
       </c>
       <c r="O17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0672268907563025</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.3449933102130747</v>
       </c>
     </row>
@@ -4435,7 +4648,7 @@
         <v>550000</v>
       </c>
       <c r="G18">
-        <v>2900</v>
+        <v>2963</v>
       </c>
       <c r="H18">
         <v>640</v>
@@ -4450,24 +4663,24 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <f t="shared" si="0"/>
-        <v>14037</v>
+        <f>G18+L17</f>
+        <v>14100</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2603932836490976</v>
+        <f t="shared" si="0"/>
+        <v>1.2660501032594056</v>
       </c>
       <c r="N18">
-        <f t="shared" si="1"/>
+        <f>N17+D18</f>
         <v>3375000</v>
       </c>
       <c r="O18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0629921259842521</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="4"/>
-        <v>1.3397881361624269</v>
+        <f t="shared" si="2"/>
+        <v>1.3458012908662975</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -4505,24 +4718,24 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <f t="shared" si="0"/>
-        <v>29037</v>
+        <f>G19+L18</f>
+        <v>29100</v>
       </c>
       <c r="M19" s="12">
-        <f t="shared" si="2"/>
-        <v>2.0686044026501391</v>
+        <f t="shared" si="0"/>
+        <v>2.0638297872340425</v>
       </c>
       <c r="N19">
-        <f t="shared" si="1"/>
+        <f>N18+D19</f>
         <v>3975000</v>
       </c>
       <c r="O19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.1777777777777778</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="4"/>
-        <v>2.4363562964546084</v>
+        <f t="shared" si="2"/>
+        <v>2.4307328605200946</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -4541,10 +4754,10 @@
       <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20">
         <v>610000</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20">
         <v>7600</v>
       </c>
       <c r="H20">
@@ -4560,25 +4773,25 @@
         <v>1</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" si="0"/>
-        <v>36637</v>
+        <f>G20+L19</f>
+        <v>36700</v>
       </c>
       <c r="M20" s="13">
-        <f t="shared" si="2"/>
-        <v>1.2617350277232497</v>
+        <f t="shared" si="0"/>
+        <v>1.261168384879725</v>
       </c>
       <c r="N20" s="1">
-        <f t="shared" si="1"/>
+        <f>N19+D20</f>
         <v>4215000</v>
       </c>
       <c r="O20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.060377358490566</v>
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1">
-        <f t="shared" si="4"/>
-        <v>1.3379152558122007</v>
+        <f t="shared" si="2"/>
+        <v>1.3373144005705764</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
@@ -4616,24 +4829,24 @@
         <v>1</v>
       </c>
       <c r="L21">
-        <f t="shared" si="0"/>
-        <v>46337</v>
+        <f>G21+L20</f>
+        <v>46400</v>
       </c>
       <c r="M21" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2647596691868876</v>
+        <f t="shared" si="0"/>
+        <v>1.2643051771117166</v>
       </c>
       <c r="N21">
-        <f t="shared" si="1"/>
+        <f>N20+D21</f>
         <v>4455000</v>
       </c>
       <c r="O21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0569395017793595</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="4"/>
-        <v>1.3367744546210165</v>
+        <f t="shared" si="2"/>
+        <v>1.3362940839935227</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -4671,24 +4884,24 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <f t="shared" si="0"/>
-        <v>58337</v>
+        <f>G22+L21</f>
+        <v>58400</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2589723115436908</v>
+        <f t="shared" si="0"/>
+        <v>1.2586206896551724</v>
       </c>
       <c r="N22">
-        <f t="shared" si="1"/>
+        <f>N21+D22</f>
         <v>4695000</v>
       </c>
       <c r="O22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0538720538720538</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="4"/>
-        <v>1.3267957357345967</v>
+        <f t="shared" si="2"/>
+        <v>1.3264251712527575</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -4711,7 +4924,7 @@
         <v>640000</v>
       </c>
       <c r="G23">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="H23">
         <v>1900</v>
@@ -4726,24 +4939,24 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <f t="shared" si="0"/>
-        <v>73837</v>
+        <f>G23+L22</f>
+        <v>74100</v>
       </c>
       <c r="M23" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2656975847232459</v>
+        <f t="shared" si="0"/>
+        <v>1.2688356164383561</v>
       </c>
       <c r="N23">
-        <f t="shared" si="1"/>
+        <f>N22+D23</f>
         <v>4935000</v>
       </c>
       <c r="O23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0511182108626198</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="4"/>
-        <v>1.3303977807474374</v>
+        <f t="shared" si="2"/>
+        <v>1.3336962230294542</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -4766,7 +4979,7 @@
         <v>650000</v>
       </c>
       <c r="G24">
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="H24">
         <v>2300</v>
@@ -4781,24 +4994,24 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <f t="shared" si="0"/>
-        <v>92837</v>
+        <f>G24+L23</f>
+        <v>95100</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2573235640667957</v>
+        <f t="shared" si="0"/>
+        <v>1.2834008097165992</v>
       </c>
       <c r="N24">
-        <f t="shared" si="1"/>
+        <f>N23+D24</f>
         <v>5175000</v>
       </c>
       <c r="O24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0486322188449848</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="4"/>
-        <v>1.3184699987934483</v>
+        <f t="shared" si="2"/>
+        <v>1.3458154387605676</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
@@ -4817,10 +5030,10 @@
       <c r="E25" s="1">
         <v>0</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25">
         <v>700000</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25">
         <v>100000</v>
       </c>
       <c r="H25">
@@ -4836,25 +5049,25 @@
         <v>5</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="0"/>
-        <v>192837</v>
+        <f>G25+L24</f>
+        <v>195100</v>
       </c>
       <c r="M25" s="13">
-        <f t="shared" si="2"/>
-        <v>2.077156737076812</v>
+        <f t="shared" si="0"/>
+        <v>2.0515247108307046</v>
       </c>
       <c r="N25" s="1">
-        <f t="shared" si="1"/>
+        <f>N24+D25</f>
         <v>6175000</v>
       </c>
       <c r="O25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.1932367149758454</v>
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1">
-        <f t="shared" si="4"/>
-        <v>2.4785396814394809</v>
+        <f t="shared" si="2"/>
+        <v>2.447954606643401</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
@@ -4874,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>700000</v>
+        <v>710000</v>
       </c>
       <c r="G26">
         <v>50000</v>
@@ -4892,24 +5105,24 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <f t="shared" si="0"/>
-        <v>242837</v>
+        <f>G26+L25</f>
+        <v>245100</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2592863402770216</v>
+        <f t="shared" si="0"/>
+        <v>1.2562788313685289</v>
       </c>
       <c r="N26">
-        <f t="shared" si="1"/>
+        <f>N25+D26</f>
         <v>6475000</v>
       </c>
       <c r="O26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.048582995951417</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="4"/>
-        <v>1.3204662434483749</v>
+        <f t="shared" si="2"/>
+        <v>1.3173126207467571</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -4929,13 +5142,13 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>700000</v>
+        <v>720000</v>
       </c>
       <c r="G27">
         <v>65000</v>
       </c>
       <c r="H27">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="I27" t="s">
         <v>23</v>
@@ -4947,24 +5160,24 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <f t="shared" si="0"/>
-        <v>307837</v>
+        <f>G27+L26</f>
+        <v>310100</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="2"/>
-        <v>1.267669259626828</v>
+        <f t="shared" si="0"/>
+        <v>1.2651978784169726</v>
       </c>
       <c r="N27">
-        <f t="shared" si="1"/>
+        <f>N26+D27</f>
         <v>6775000</v>
       </c>
       <c r="O27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0463320463320462</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="4"/>
-        <v>1.3264029704975688</v>
+        <f t="shared" si="2"/>
+        <v>1.3238170851389943</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -4984,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>700000</v>
+        <v>730000</v>
       </c>
       <c r="G28">
         <v>80000</v>
@@ -5002,24 +5215,24 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <f t="shared" si="0"/>
-        <v>387837</v>
+        <f>G28+L27</f>
+        <v>390100</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="2"/>
-        <v>1.259877792468092</v>
+        <f t="shared" si="0"/>
+        <v>1.2579812963560142</v>
       </c>
       <c r="N28">
-        <f t="shared" si="1"/>
+        <f>N27+D28</f>
         <v>7075000</v>
       </c>
       <c r="O28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0442804428044281</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="4"/>
-        <v>1.3156657389980444</v>
+        <f t="shared" si="2"/>
+        <v>1.3136852651983471</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
@@ -5039,13 +5252,13 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>700000</v>
+        <v>740000</v>
       </c>
       <c r="G29">
         <v>100000</v>
       </c>
       <c r="H29">
-        <v>6500</v>
+        <v>6800</v>
       </c>
       <c r="I29" t="s">
         <v>25</v>
@@ -5057,24 +5270,24 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <f t="shared" si="0"/>
-        <v>487837</v>
+        <f>G29+L28</f>
+        <v>490100</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2578402782612284</v>
+        <f t="shared" si="0"/>
+        <v>1.2563445270443476</v>
       </c>
       <c r="N29">
-        <f t="shared" si="1"/>
+        <f>N28+D29</f>
         <v>7375000</v>
       </c>
       <c r="O29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0424028268551238</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="4"/>
-        <v>1.31117626179174</v>
+        <f t="shared" si="2"/>
+        <v>1.3096170864949914</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
@@ -5094,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>700000</v>
+        <v>750000</v>
       </c>
       <c r="G30">
         <v>130000</v>
@@ -5112,24 +5325,24 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <f t="shared" si="0"/>
-        <v>617837</v>
+        <f>G30+L29</f>
+        <v>620100</v>
       </c>
       <c r="M30" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2664824521305271</v>
+        <f t="shared" si="0"/>
+        <v>1.2652519893899203</v>
       </c>
       <c r="N30">
-        <f t="shared" si="1"/>
+        <f>N29+D30</f>
         <v>7675000</v>
       </c>
       <c r="O30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0406779661016949</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="4"/>
-        <v>1.3180003823866842</v>
+        <f t="shared" si="2"/>
+        <v>1.3167198669244256</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
@@ -5149,10 +5362,10 @@
         <v>0</v>
       </c>
       <c r="F31">
+        <v>800000</v>
+      </c>
+      <c r="G31">
         <v>700000</v>
-      </c>
-      <c r="G31">
-        <v>160000</v>
       </c>
       <c r="H31">
         <v>30000</v>
@@ -5167,24 +5380,24 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <f t="shared" si="0"/>
-        <v>777837</v>
+        <f>G31+L30</f>
+        <v>1320100</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="2"/>
-        <v>1.2589679802277947</v>
+        <f t="shared" si="0"/>
+        <v>2.1288501854539592</v>
       </c>
       <c r="N31">
-        <f t="shared" si="1"/>
+        <f>N30+D31</f>
         <v>9875000</v>
       </c>
       <c r="O31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2866449511400651</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="4"/>
-        <v>1.6198447954070971</v>
+        <f t="shared" si="2"/>
+        <v>2.7390743428479278</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
@@ -5204,10 +5417,10 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>700000</v>
+        <v>810000</v>
       </c>
       <c r="G32">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="H32">
         <v>14000</v>
@@ -5222,24 +5435,24 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <f t="shared" si="0"/>
-        <v>977837</v>
+        <f>G32+L31</f>
+        <v>1620100</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="2"/>
-        <v>1.257123279041753</v>
+        <f t="shared" si="0"/>
+        <v>1.2272555109461405</v>
       </c>
       <c r="N32">
-        <f t="shared" si="1"/>
+        <f>N31+D32</f>
         <v>10275000</v>
       </c>
       <c r="O32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.040506329113924</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="4"/>
-        <v>1.3080447283193937</v>
+        <f t="shared" si="2"/>
+        <v>1.2769671265794018</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
@@ -5259,10 +5472,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>700000</v>
+        <v>820000</v>
       </c>
       <c r="G33">
-        <v>17000</v>
+        <v>450000</v>
       </c>
       <c r="H33">
         <v>17000</v>
@@ -5277,24 +5490,24 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <f t="shared" si="0"/>
-        <v>994837</v>
+        <f>G33+L32</f>
+        <v>2070100</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="2"/>
-        <v>1.0173853106397079</v>
+        <f t="shared" si="0"/>
+        <v>1.2777606320597494</v>
       </c>
       <c r="N33">
-        <f t="shared" si="1"/>
+        <f>N32+D33</f>
         <v>10675000</v>
       </c>
       <c r="O33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0389294403892944</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="4"/>
-        <v>1.0569915514432002</v>
+        <f t="shared" si="2"/>
+        <v>1.3275031384173066</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
@@ -5314,10 +5527,10 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>700000</v>
+        <v>830000</v>
       </c>
       <c r="G34">
-        <v>20000</v>
+        <v>500000</v>
       </c>
       <c r="H34">
         <v>20000</v>
@@ -5332,24 +5545,24 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <f t="shared" si="0"/>
-        <v>1014837</v>
+        <f>G34+L33</f>
+        <v>2570100</v>
       </c>
       <c r="M34" s="12">
-        <f t="shared" si="2"/>
-        <v>1.0201037958982224</v>
+        <f t="shared" si="0"/>
+        <v>1.2415342253997392</v>
       </c>
       <c r="N34">
-        <f t="shared" si="1"/>
+        <f>N33+D34</f>
         <v>11075000</v>
       </c>
       <c r="O34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0374707259953162</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="4"/>
-        <v>1.0583278257211066</v>
+        <f t="shared" si="2"/>
+        <v>1.2880554141735001</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
@@ -5369,10 +5582,10 @@
         <v>0</v>
       </c>
       <c r="F35">
+        <v>840000</v>
+      </c>
+      <c r="G35">
         <v>700000</v>
-      </c>
-      <c r="G35">
-        <v>23000</v>
       </c>
       <c r="H35">
         <v>23000</v>
@@ -5387,24 +5600,24 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <f t="shared" si="0"/>
-        <v>1037837</v>
+        <f>G35+L34</f>
+        <v>3270100</v>
       </c>
       <c r="M35" s="12">
-        <f t="shared" si="2"/>
-        <v>1.0226637381175498</v>
+        <f t="shared" si="0"/>
+        <v>1.2723629430761449</v>
       </c>
       <c r="N35">
-        <f t="shared" si="1"/>
+        <f>N34+D35</f>
         <v>11475000</v>
       </c>
       <c r="O35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0361173814898419</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="4"/>
-        <v>1.0595996744829692</v>
+        <f t="shared" si="2"/>
+        <v>1.318317360884764</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
@@ -5424,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>700000</v>
+        <v>850000</v>
       </c>
       <c r="G36">
-        <v>27000</v>
+        <v>800000</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -5442,24 +5655,24 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <f t="shared" si="0"/>
-        <v>1064837</v>
+        <f>G36+L35</f>
+        <v>4070100</v>
       </c>
       <c r="M36" s="12">
-        <f t="shared" si="2"/>
-        <v>1.0260156460022143</v>
+        <f t="shared" si="0"/>
+        <v>1.2446408366716615</v>
       </c>
       <c r="N36">
-        <f t="shared" si="1"/>
+        <f>N35+D36</f>
         <v>11875000</v>
       </c>
       <c r="O36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0348583877995643</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="4"/>
-        <v>1.06178089727898</v>
+        <f t="shared" si="2"/>
+        <v>1.2880270096275364</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
@@ -5479,10 +5692,10 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>700000</v>
+        <v>900000</v>
       </c>
       <c r="G37">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="H37">
         <v>100000</v>
@@ -5497,24 +5710,24 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <f t="shared" si="0"/>
-        <v>1164837</v>
+        <f>G37+L36</f>
+        <v>9070100</v>
       </c>
       <c r="M37" s="12">
-        <f t="shared" si="2"/>
-        <v>1.0939110868611817</v>
+        <f t="shared" si="0"/>
+        <v>2.2284710449374709</v>
       </c>
       <c r="N37">
-        <f t="shared" si="1"/>
+        <f>N36+D37</f>
         <v>16375000</v>
       </c>
       <c r="O37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3789473684210527</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="4"/>
-        <v>1.50844581451384</v>
+        <f t="shared" si="2"/>
+        <v>3.072944283019039</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
@@ -5552,24 +5765,33 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <f t="shared" si="0"/>
-        <v>1164836</v>
+        <f>G38+L37</f>
+        <v>9070099</v>
       </c>
       <c r="M38" s="12">
-        <f t="shared" si="2"/>
-        <v>0.9999991415107865</v>
+        <f t="shared" si="0"/>
+        <v>0.99999988974763232</v>
       </c>
       <c r="N38">
-        <f t="shared" si="1"/>
+        <f>N37+D38</f>
         <v>16374999</v>
       </c>
       <c r="O38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.99999993893129768</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="4"/>
-        <v>0.99999908044213659</v>
+        <f t="shared" si="2"/>
+        <v>0.99999982867893678</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F39" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39">
+        <f>SUM(G2:G37)</f>
+        <v>9070000</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">

--- a/정기/BM/각성 절멸타 수치/각성 절멸타 수치.xlsx
+++ b/정기/BM/각성 절멸타 수치/각성 절멸타 수치.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\BM\각성 절멸타 수치\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44DFDE6-AD02-4565-A416-30D7432D8076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87002D6-B399-4B8B-BA1A-330B4349D4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="465" windowWidth="19200" windowHeight="15480" xr2:uid="{3E321328-0C01-4213-932A-34E838058470}"/>
+    <workbookView xWindow="4800" yWindow="1890" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{3E321328-0C01-4213-932A-34E838058470}"/>
   </bookViews>
   <sheets>
     <sheet name="보스체력" sheetId="2" r:id="rId1"/>
     <sheet name="패기" sheetId="1" r:id="rId2"/>
     <sheet name="무기" sheetId="3" r:id="rId3"/>
     <sheet name="갑옷" sheetId="4" r:id="rId4"/>
-    <sheet name="절멸타" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="37">
   <si>
     <t>아이디</t>
   </si>
@@ -79,11 +78,11 @@
   </si>
   <si>
     <t>패기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ㅠㅜ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>각성 보유 효과</t>
@@ -149,343 +148,22 @@
     <t>-</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>스탯이름</t>
-  </si>
-  <si>
-    <t>고정값</t>
-  </si>
-  <si>
-    <t>고정값조정</t>
-  </si>
-  <si>
-    <t>상승값</t>
-  </si>
-  <si>
-    <t>최대값</t>
-  </si>
-  <si>
-    <t>예측(사용X)</t>
-  </si>
-  <si>
-    <t>1A   100만</t>
-  </si>
-  <si>
-    <t>랭킹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테이지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20시간</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력</t>
-  </si>
-  <si>
-    <t>52C_4만육성</t>
-  </si>
-  <si>
-    <t>10A   1000만</t>
-  </si>
-  <si>
-    <t>생명력</t>
-  </si>
-  <si>
-    <t>100A   1억</t>
-  </si>
-  <si>
-    <t>950b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>회심타확률</t>
-  </si>
-  <si>
-    <t>51C</t>
-  </si>
-  <si>
-    <t>125c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1B   10억</t>
-  </si>
-  <si>
-    <t>회심타데미지</t>
-  </si>
-  <si>
-    <t>110C</t>
-  </si>
-  <si>
-    <t>272c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10B   100억</t>
-  </si>
-  <si>
-    <t>50b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>100b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>150b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>200b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>250b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>51C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>흑천검</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>절멸타확률</t>
-  </si>
-  <si>
-    <t>300C</t>
-  </si>
-  <si>
-    <t>376c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>100B   1000억</t>
-  </si>
-  <si>
-    <t>절멸타데미지</t>
-  </si>
-  <si>
-    <t>600C</t>
-  </si>
-  <si>
-    <t>810c</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1C   1조</t>
-  </si>
-  <si>
-    <t>10C   10조</t>
-  </si>
-  <si>
-    <t>23b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>44b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>66b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>87b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>11b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>등차수열항</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>등차합</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>100C   100조</t>
-  </si>
-  <si>
-    <t>개수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>노말</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고급</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>비용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>희귀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전설</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>어빌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>다이아</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>돈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>신화</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>다야</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>한번당 가격</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>단계</t>
-  </si>
-  <si>
-    <t>확률(%)</t>
-  </si>
-  <si>
-    <t>확률(소수)</t>
-  </si>
-  <si>
-    <t>합</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>현금</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>생명력</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>근력증폭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어증폭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격숙련도</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬숙련도</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>금화획득량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강화석획득량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치획등량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>노다지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>67b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>12시간</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>회심타</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>92b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>회심타데미지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>랭킹2등</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드b</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강화석</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>수정 각성 보유 예정 수치1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> </t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="0.000%"/>
-    <numFmt numFmtId="177" formatCode="0.000"/>
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -501,17 +179,8 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -521,18 +190,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,64 +203,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="백분율" xfId="2" builtinId="5"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+  <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2212,14 +1831,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22727E31-19EA-48A7-B6B9-1C0D6FA6B8D4}">
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
@@ -3424,18 +3043,18 @@
         <v>2000000</v>
       </c>
       <c r="E27">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27">
         <f t="shared" si="4"/>
-        <v>190100</v>
+        <v>195100</v>
       </c>
       <c r="H27">
         <f t="shared" si="1"/>
-        <v>1.3568879371877232</v>
+        <v>1.3925767309064954</v>
       </c>
       <c r="J27">
         <f t="shared" si="0"/>
@@ -3447,7 +3066,7 @@
       </c>
       <c r="M27">
         <f t="shared" si="3"/>
-        <v>1.5096415813511681</v>
+        <v>1.5493480932225823</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -3464,18 +3083,18 @@
         <v>3000000</v>
       </c>
       <c r="E28">
-        <v>65000</v>
+        <v>70000</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
         <f t="shared" si="4"/>
-        <v>255100</v>
+        <v>265100</v>
       </c>
       <c r="H28">
         <f t="shared" si="1"/>
-        <v>1.341925302472383</v>
+        <v>1.3587903639159404</v>
       </c>
       <c r="J28">
         <f t="shared" si="0"/>
@@ -3487,7 +3106,7 @@
       </c>
       <c r="M28">
         <f t="shared" si="3"/>
-        <v>1.545600117753031</v>
+        <v>1.565024925456596</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
@@ -3504,18 +3123,18 @@
         <v>4000000</v>
       </c>
       <c r="E29">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29">
         <f t="shared" si="4"/>
-        <v>345100</v>
+        <v>350100</v>
       </c>
       <c r="H29">
         <f t="shared" si="1"/>
-        <v>1.3528028224225794</v>
+        <v>1.3206337231233496</v>
       </c>
       <c r="J29">
         <f t="shared" si="0"/>
@@ -3527,7 +3146,7 @@
       </c>
       <c r="M29">
         <f t="shared" si="3"/>
-        <v>1.5904941992138131</v>
+        <v>1.5526728959305061</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
@@ -3544,18 +3163,18 @@
         <v>5000000</v>
       </c>
       <c r="E30">
-        <v>120000</v>
+        <v>105000</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30">
         <f t="shared" si="4"/>
-        <v>465100</v>
+        <v>455100</v>
       </c>
       <c r="H30">
         <f t="shared" si="1"/>
-        <v>1.3477252970153579</v>
+        <v>1.2999143101970865</v>
       </c>
       <c r="J30">
         <f t="shared" si="0"/>
@@ -3567,7 +3186,7 @@
       </c>
       <c r="M30">
         <f t="shared" si="3"/>
-        <v>1.5994887752649967</v>
+        <v>1.542746398372967</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
@@ -3584,18 +3203,18 @@
         <v>7000000</v>
       </c>
       <c r="E31">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31">
         <f t="shared" si="4"/>
-        <v>615100</v>
+        <v>575100</v>
       </c>
       <c r="H31">
         <f t="shared" si="1"/>
-        <v>1.3225112878950764</v>
+        <v>1.2636783124588002</v>
       </c>
       <c r="J31">
         <f t="shared" si="0"/>
@@ -3607,7 +3226,7 @@
       </c>
       <c r="M31">
         <f t="shared" si="3"/>
-        <v>1.6139444419249285</v>
+        <v>1.5421468288713474</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
@@ -3624,18 +3243,18 @@
         <v>30000000</v>
       </c>
       <c r="E32">
-        <v>600000</v>
+        <v>550000</v>
       </c>
       <c r="F32">
         <v>4</v>
       </c>
       <c r="G32">
         <f t="shared" si="4"/>
-        <v>1215100</v>
+        <v>1125100</v>
       </c>
       <c r="H32">
         <f t="shared" si="1"/>
-        <v>1.9754511461550968</v>
+        <v>1.9563554164493131</v>
       </c>
       <c r="J32">
         <f t="shared" si="0"/>
@@ -3647,7 +3266,7 @@
       </c>
       <c r="M32">
         <f t="shared" si="3"/>
-        <v>3.5042131651143014</v>
+        <v>3.4703396332060525</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -3671,11 +3290,11 @@
       </c>
       <c r="G33">
         <f t="shared" si="4"/>
-        <v>1215099</v>
+        <v>1125099</v>
       </c>
       <c r="H33">
         <f t="shared" si="1"/>
-        <v>0.99999917702246732</v>
+        <v>0.99999911119011642</v>
       </c>
       <c r="J33">
         <f t="shared" si="0"/>
@@ -3687,11 +3306,21 @@
       </c>
       <c r="M33">
         <f t="shared" si="3"/>
-        <v>0.99999916248034626</v>
+        <v>0.99999909664799624</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D34">
+        <f>SUM(D3:D33)</f>
+        <v>68718999</v>
+      </c>
+      <c r="E34">
+        <f>SUM(E3:E33)</f>
+        <v>1124999</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3727,7 +3356,7 @@
         <v>16</v>
       </c>
       <c r="H1" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
         <v>17</v>
@@ -3780,15 +3409,15 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <f>G2+L1</f>
+        <f t="shared" ref="L2:L38" si="0">G2+L1</f>
         <v>126</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="2">
         <f>L2/L1</f>
         <v>1.26</v>
       </c>
       <c r="N2">
-        <f>N1+D2</f>
+        <f t="shared" ref="N2:N38" si="1">N1+D2</f>
         <v>675000</v>
       </c>
       <c r="O2">
@@ -3835,23 +3464,23 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <f>G3+L2</f>
+        <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="M3" s="12">
-        <f t="shared" ref="M3:M38" si="0">L3/L2</f>
+      <c r="M3" s="2">
+        <f t="shared" ref="M3:M38" si="2">L3/L2</f>
         <v>1.2698412698412698</v>
       </c>
       <c r="N3">
-        <f>N2+D3</f>
+        <f t="shared" si="1"/>
         <v>750000</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O38" si="1">N3/N2</f>
+        <f t="shared" ref="O3:O38" si="3">N3/N2</f>
         <v>1.1111111111111112</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q38" si="2">O3*M3</f>
+        <f t="shared" ref="Q3:Q38" si="4">O3*M3</f>
         <v>1.4109347442680775</v>
       </c>
     </row>
@@ -3890,23 +3519,23 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <f>G4+L3</f>
+        <f t="shared" si="0"/>
         <v>202</v>
       </c>
-      <c r="M4" s="12">
-        <f t="shared" si="0"/>
+      <c r="M4" s="2">
+        <f t="shared" si="2"/>
         <v>1.2625</v>
       </c>
       <c r="N4">
-        <f>N3+D4</f>
+        <f t="shared" si="1"/>
         <v>825000</v>
       </c>
       <c r="O4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3887500000000002</v>
       </c>
     </row>
@@ -3945,23 +3574,23 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <f>G5+L4</f>
+        <f t="shared" si="0"/>
         <v>255</v>
       </c>
-      <c r="M5" s="12">
-        <f t="shared" si="0"/>
+      <c r="M5" s="2">
+        <f t="shared" si="2"/>
         <v>1.2623762376237624</v>
       </c>
       <c r="N5">
-        <f>N4+D5</f>
+        <f t="shared" si="1"/>
         <v>900000</v>
       </c>
       <c r="O5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0909090909090908</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3771377137713769</v>
       </c>
     </row>
@@ -4000,23 +3629,23 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <f>G6+L5</f>
+        <f t="shared" si="0"/>
         <v>322</v>
       </c>
-      <c r="M6" s="12">
-        <f t="shared" si="0"/>
+      <c r="M6" s="2">
+        <f t="shared" si="2"/>
         <v>1.2627450980392156</v>
       </c>
       <c r="N6">
-        <f>N5+D6</f>
+        <f t="shared" si="1"/>
         <v>975000</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0833333333333333</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3679738562091501</v>
       </c>
     </row>
@@ -4055,23 +3684,23 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <f>G7+L6</f>
+        <f t="shared" si="0"/>
         <v>652</v>
       </c>
-      <c r="M7" s="12">
-        <f t="shared" si="0"/>
+      <c r="M7" s="2">
+        <f t="shared" si="2"/>
         <v>2.0248447204968945</v>
       </c>
       <c r="N7">
-        <f>N6+D7</f>
+        <f t="shared" si="1"/>
         <v>1275000</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3076923076923077</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.6478738652651699</v>
       </c>
     </row>
@@ -4110,23 +3739,23 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <f>G8+L7</f>
+        <f t="shared" si="0"/>
         <v>822</v>
       </c>
-      <c r="M8" s="12">
-        <f t="shared" si="0"/>
+      <c r="M8" s="2">
+        <f t="shared" si="2"/>
         <v>1.2607361963190185</v>
       </c>
       <c r="N8">
-        <f>N7+D8</f>
+        <f t="shared" si="1"/>
         <v>1475000</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1568627450980393</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4584987369180804</v>
       </c>
     </row>
@@ -4165,23 +3794,23 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <f>G9+L8</f>
+        <f t="shared" si="0"/>
         <v>1037</v>
       </c>
-      <c r="M9" s="12">
-        <f t="shared" si="0"/>
+      <c r="M9" s="2">
+        <f t="shared" si="2"/>
         <v>1.2615571776155718</v>
       </c>
       <c r="N9">
-        <f>N8+D9</f>
+        <f t="shared" si="1"/>
         <v>1675000</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1355932203389831</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4326157779702258</v>
       </c>
       <c r="W9">
@@ -4223,23 +3852,23 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <f>G10+L9</f>
+        <f t="shared" si="0"/>
         <v>1307</v>
       </c>
-      <c r="M10" s="12">
-        <f t="shared" si="0"/>
+      <c r="M10" s="2">
+        <f t="shared" si="2"/>
         <v>1.2603664416586307</v>
       </c>
       <c r="N10">
-        <f>N9+D10</f>
+        <f t="shared" si="1"/>
         <v>1775000</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0597014925373134</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3356121993695935</v>
       </c>
     </row>
@@ -4278,23 +3907,23 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <f>G11+L10</f>
+        <f t="shared" si="0"/>
         <v>1657</v>
       </c>
-      <c r="M11" s="12">
-        <f t="shared" si="0"/>
+      <c r="M11" s="2">
+        <f t="shared" si="2"/>
         <v>1.2677888293802602</v>
       </c>
       <c r="N11">
-        <f>N10+D11</f>
+        <f t="shared" si="1"/>
         <v>1875000</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.056338028169014</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3392135521622466</v>
       </c>
     </row>
@@ -4333,23 +3962,23 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <f>G12+L11</f>
+        <f t="shared" si="0"/>
         <v>2087</v>
       </c>
-      <c r="M12" s="12">
-        <f t="shared" si="0"/>
+      <c r="M12" s="2">
+        <f t="shared" si="2"/>
         <v>1.2595051297525648</v>
       </c>
       <c r="N12">
-        <f>N11+D12</f>
+        <f t="shared" si="1"/>
         <v>1975000</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0533333333333332</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3266787366727015</v>
       </c>
     </row>
@@ -4388,23 +4017,23 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <f>G13+L12</f>
+        <f t="shared" si="0"/>
         <v>4387</v>
       </c>
-      <c r="M13" s="12">
-        <f t="shared" si="0"/>
+      <c r="M13" s="2">
+        <f t="shared" si="2"/>
         <v>2.1020603737422139</v>
       </c>
       <c r="N13">
-        <f>N12+D13</f>
+        <f t="shared" si="1"/>
         <v>2375000</v>
       </c>
       <c r="O13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2025316455696202</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.5277941203229153</v>
       </c>
     </row>
@@ -4443,23 +4072,23 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <f>G14+L13</f>
+        <f t="shared" si="0"/>
         <v>5537</v>
       </c>
-      <c r="M14" s="12">
-        <f t="shared" si="0"/>
+      <c r="M14" s="2">
+        <f t="shared" si="2"/>
         <v>1.2621381354000456</v>
       </c>
       <c r="N14">
-        <f>N13+D14</f>
+        <f t="shared" si="1"/>
         <v>2575000</v>
       </c>
       <c r="O14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0842105263157895</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3684234520653127</v>
       </c>
     </row>
@@ -4498,23 +4127,23 @@
         <v>1</v>
       </c>
       <c r="L15">
-        <f>G15+L14</f>
+        <f t="shared" si="0"/>
         <v>6987</v>
       </c>
-      <c r="M15" s="12">
-        <f t="shared" si="0"/>
+      <c r="M15" s="2">
+        <f t="shared" si="2"/>
         <v>1.2618746613689724</v>
       </c>
       <c r="N15">
-        <f>N14+D15</f>
+        <f t="shared" si="1"/>
         <v>2775000</v>
       </c>
       <c r="O15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0776699029126213</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3598843438053974</v>
       </c>
     </row>
@@ -4553,23 +4182,23 @@
         <v>1</v>
       </c>
       <c r="L16">
-        <f>G16+L15</f>
+        <f t="shared" si="0"/>
         <v>8837</v>
       </c>
-      <c r="M16" s="12">
-        <f t="shared" si="0"/>
+      <c r="M16" s="2">
+        <f t="shared" si="2"/>
         <v>1.264777443824245</v>
       </c>
       <c r="N16">
-        <f>N15+D16</f>
+        <f t="shared" si="1"/>
         <v>2975000</v>
       </c>
       <c r="O16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.072072072072072</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.355932574910677</v>
       </c>
     </row>
@@ -4608,23 +4237,23 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <f>G17+L16</f>
+        <f t="shared" si="0"/>
         <v>11137</v>
       </c>
-      <c r="M17" s="12">
-        <f t="shared" si="0"/>
+      <c r="M17" s="2">
+        <f t="shared" si="2"/>
         <v>1.2602693221681567</v>
       </c>
       <c r="N17">
-        <f>N16+D17</f>
+        <f t="shared" si="1"/>
         <v>3175000</v>
       </c>
       <c r="O17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0672268907563025</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3449933102130747</v>
       </c>
     </row>
@@ -4663,23 +4292,23 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <f>G18+L17</f>
+        <f t="shared" si="0"/>
         <v>14100</v>
       </c>
-      <c r="M18" s="12">
-        <f t="shared" si="0"/>
+      <c r="M18" s="2">
+        <f t="shared" si="2"/>
         <v>1.2660501032594056</v>
       </c>
       <c r="N18">
-        <f>N17+D18</f>
+        <f t="shared" si="1"/>
         <v>3375000</v>
       </c>
       <c r="O18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0629921259842521</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3458012908662975</v>
       </c>
     </row>
@@ -4718,23 +4347,23 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <f>G19+L18</f>
+        <f t="shared" si="0"/>
         <v>29100</v>
       </c>
-      <c r="M19" s="12">
-        <f t="shared" si="0"/>
+      <c r="M19" s="2">
+        <f t="shared" si="2"/>
         <v>2.0638297872340425</v>
       </c>
       <c r="N19">
-        <f>N18+D19</f>
+        <f t="shared" si="1"/>
         <v>3975000</v>
       </c>
       <c r="O19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1777777777777778</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.4307328605200946</v>
       </c>
     </row>
@@ -4773,24 +4402,24 @@
         <v>1</v>
       </c>
       <c r="L20" s="1">
-        <f>G20+L19</f>
+        <f t="shared" si="0"/>
         <v>36700</v>
       </c>
-      <c r="M20" s="13">
-        <f t="shared" si="0"/>
+      <c r="M20" s="3">
+        <f t="shared" si="2"/>
         <v>1.261168384879725</v>
       </c>
       <c r="N20" s="1">
-        <f>N19+D20</f>
+        <f t="shared" si="1"/>
         <v>4215000</v>
       </c>
       <c r="O20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.060377358490566</v>
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3373144005705764</v>
       </c>
     </row>
@@ -4829,23 +4458,23 @@
         <v>1</v>
       </c>
       <c r="L21">
-        <f>G21+L20</f>
+        <f t="shared" si="0"/>
         <v>46400</v>
       </c>
-      <c r="M21" s="12">
-        <f t="shared" si="0"/>
+      <c r="M21" s="2">
+        <f t="shared" si="2"/>
         <v>1.2643051771117166</v>
       </c>
       <c r="N21">
-        <f>N20+D21</f>
+        <f t="shared" si="1"/>
         <v>4455000</v>
       </c>
       <c r="O21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0569395017793595</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3362940839935227</v>
       </c>
     </row>
@@ -4884,23 +4513,23 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <f>G22+L21</f>
+        <f t="shared" si="0"/>
         <v>58400</v>
       </c>
-      <c r="M22" s="12">
-        <f t="shared" si="0"/>
+      <c r="M22" s="2">
+        <f t="shared" si="2"/>
         <v>1.2586206896551724</v>
       </c>
       <c r="N22">
-        <f>N21+D22</f>
+        <f t="shared" si="1"/>
         <v>4695000</v>
       </c>
       <c r="O22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0538720538720538</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3264251712527575</v>
       </c>
     </row>
@@ -4939,23 +4568,23 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <f>G23+L22</f>
+        <f t="shared" si="0"/>
         <v>74100</v>
       </c>
-      <c r="M23" s="12">
-        <f t="shared" si="0"/>
+      <c r="M23" s="2">
+        <f t="shared" si="2"/>
         <v>1.2688356164383561</v>
       </c>
       <c r="N23">
-        <f>N22+D23</f>
+        <f t="shared" si="1"/>
         <v>4935000</v>
       </c>
       <c r="O23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0511182108626198</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3336962230294542</v>
       </c>
     </row>
@@ -4994,23 +4623,23 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <f>G24+L23</f>
+        <f t="shared" si="0"/>
         <v>95100</v>
       </c>
-      <c r="M24" s="12">
-        <f t="shared" si="0"/>
+      <c r="M24" s="2">
+        <f t="shared" si="2"/>
         <v>1.2834008097165992</v>
       </c>
       <c r="N24">
-        <f>N23+D24</f>
+        <f t="shared" si="1"/>
         <v>5175000</v>
       </c>
       <c r="O24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0486322188449848</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3458154387605676</v>
       </c>
     </row>
@@ -5049,24 +4678,24 @@
         <v>5</v>
       </c>
       <c r="L25" s="1">
-        <f>G25+L24</f>
+        <f t="shared" si="0"/>
         <v>195100</v>
       </c>
-      <c r="M25" s="13">
-        <f t="shared" si="0"/>
+      <c r="M25" s="3">
+        <f t="shared" si="2"/>
         <v>2.0515247108307046</v>
       </c>
       <c r="N25" s="1">
-        <f>N24+D25</f>
+        <f t="shared" si="1"/>
         <v>6175000</v>
       </c>
       <c r="O25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.1932367149758454</v>
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.447954606643401</v>
       </c>
     </row>
@@ -5105,23 +4734,23 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <f>G26+L25</f>
+        <f t="shared" si="0"/>
         <v>245100</v>
       </c>
-      <c r="M26" s="12">
-        <f t="shared" si="0"/>
+      <c r="M26" s="2">
+        <f t="shared" si="2"/>
         <v>1.2562788313685289</v>
       </c>
       <c r="N26">
-        <f>N25+D26</f>
+        <f t="shared" si="1"/>
         <v>6475000</v>
       </c>
       <c r="O26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.048582995951417</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3173126207467571</v>
       </c>
     </row>
@@ -5160,23 +4789,23 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <f>G27+L26</f>
+        <f t="shared" si="0"/>
         <v>310100</v>
       </c>
-      <c r="M27" s="12">
-        <f t="shared" si="0"/>
+      <c r="M27" s="2">
+        <f t="shared" si="2"/>
         <v>1.2651978784169726</v>
       </c>
       <c r="N27">
-        <f>N26+D27</f>
+        <f t="shared" si="1"/>
         <v>6775000</v>
       </c>
       <c r="O27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0463320463320462</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3238170851389943</v>
       </c>
     </row>
@@ -5215,23 +4844,23 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <f>G28+L27</f>
+        <f t="shared" si="0"/>
         <v>390100</v>
       </c>
-      <c r="M28" s="12">
-        <f t="shared" si="0"/>
+      <c r="M28" s="2">
+        <f t="shared" si="2"/>
         <v>1.2579812963560142</v>
       </c>
       <c r="N28">
-        <f>N27+D28</f>
+        <f t="shared" si="1"/>
         <v>7075000</v>
       </c>
       <c r="O28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0442804428044281</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3136852651983471</v>
       </c>
     </row>
@@ -5270,23 +4899,23 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <f>G29+L28</f>
+        <f t="shared" si="0"/>
         <v>490100</v>
       </c>
-      <c r="M29" s="12">
-        <f t="shared" si="0"/>
+      <c r="M29" s="2">
+        <f t="shared" si="2"/>
         <v>1.2563445270443476</v>
       </c>
       <c r="N29">
-        <f>N28+D29</f>
+        <f t="shared" si="1"/>
         <v>7375000</v>
       </c>
       <c r="O29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0424028268551238</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3096170864949914</v>
       </c>
     </row>
@@ -5325,23 +4954,23 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <f>G30+L29</f>
+        <f t="shared" si="0"/>
         <v>620100</v>
       </c>
-      <c r="M30" s="12">
-        <f t="shared" si="0"/>
+      <c r="M30" s="2">
+        <f t="shared" si="2"/>
         <v>1.2652519893899203</v>
       </c>
       <c r="N30">
-        <f>N29+D30</f>
+        <f t="shared" si="1"/>
         <v>7675000</v>
       </c>
       <c r="O30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0406779661016949</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3167198669244256</v>
       </c>
     </row>
@@ -5380,23 +5009,23 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <f>G31+L30</f>
+        <f t="shared" si="0"/>
         <v>1320100</v>
       </c>
-      <c r="M31" s="12">
-        <f t="shared" si="0"/>
+      <c r="M31" s="2">
+        <f t="shared" si="2"/>
         <v>2.1288501854539592</v>
       </c>
       <c r="N31">
-        <f>N30+D31</f>
+        <f t="shared" si="1"/>
         <v>9875000</v>
       </c>
       <c r="O31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.2866449511400651</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.7390743428479278</v>
       </c>
     </row>
@@ -5435,23 +5064,23 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <f>G32+L31</f>
+        <f t="shared" si="0"/>
         <v>1620100</v>
       </c>
-      <c r="M32" s="12">
-        <f t="shared" si="0"/>
+      <c r="M32" s="2">
+        <f t="shared" si="2"/>
         <v>1.2272555109461405</v>
       </c>
       <c r="N32">
-        <f>N31+D32</f>
+        <f t="shared" si="1"/>
         <v>10275000</v>
       </c>
       <c r="O32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.040506329113924</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2769671265794018</v>
       </c>
     </row>
@@ -5490,23 +5119,23 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <f>G33+L32</f>
+        <f t="shared" si="0"/>
         <v>2070100</v>
       </c>
-      <c r="M33" s="12">
-        <f t="shared" si="0"/>
+      <c r="M33" s="2">
+        <f t="shared" si="2"/>
         <v>1.2777606320597494</v>
       </c>
       <c r="N33">
-        <f>N32+D33</f>
+        <f t="shared" si="1"/>
         <v>10675000</v>
       </c>
       <c r="O33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0389294403892944</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3275031384173066</v>
       </c>
     </row>
@@ -5545,23 +5174,23 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <f>G34+L33</f>
+        <f t="shared" si="0"/>
         <v>2570100</v>
       </c>
-      <c r="M34" s="12">
-        <f t="shared" si="0"/>
+      <c r="M34" s="2">
+        <f t="shared" si="2"/>
         <v>1.2415342253997392</v>
       </c>
       <c r="N34">
-        <f>N33+D34</f>
+        <f t="shared" si="1"/>
         <v>11075000</v>
       </c>
       <c r="O34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0374707259953162</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2880554141735001</v>
       </c>
     </row>
@@ -5600,23 +5229,23 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <f>G35+L34</f>
+        <f t="shared" si="0"/>
         <v>3270100</v>
       </c>
-      <c r="M35" s="12">
-        <f t="shared" si="0"/>
+      <c r="M35" s="2">
+        <f t="shared" si="2"/>
         <v>1.2723629430761449</v>
       </c>
       <c r="N35">
-        <f>N34+D35</f>
+        <f t="shared" si="1"/>
         <v>11475000</v>
       </c>
       <c r="O35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0361173814898419</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.318317360884764</v>
       </c>
     </row>
@@ -5655,23 +5284,23 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <f>G36+L35</f>
+        <f t="shared" si="0"/>
         <v>4070100</v>
       </c>
-      <c r="M36" s="12">
-        <f t="shared" si="0"/>
+      <c r="M36" s="2">
+        <f t="shared" si="2"/>
         <v>1.2446408366716615</v>
       </c>
       <c r="N36">
-        <f>N35+D36</f>
+        <f t="shared" si="1"/>
         <v>11875000</v>
       </c>
       <c r="O36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0348583877995643</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2880270096275364</v>
       </c>
     </row>
@@ -5710,23 +5339,23 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <f>G37+L36</f>
+        <f t="shared" si="0"/>
         <v>9070100</v>
       </c>
-      <c r="M37" s="12">
-        <f t="shared" si="0"/>
+      <c r="M37" s="2">
+        <f t="shared" si="2"/>
         <v>2.2284710449374709</v>
       </c>
       <c r="N37">
-        <f>N36+D37</f>
+        <f t="shared" si="1"/>
         <v>16375000</v>
       </c>
       <c r="O37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3789473684210527</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.072944283019039</v>
       </c>
     </row>
@@ -5765,29 +5394,29 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <f>G38+L37</f>
+        <f t="shared" si="0"/>
         <v>9070099</v>
       </c>
-      <c r="M38" s="12">
-        <f t="shared" si="0"/>
+      <c r="M38" s="2">
+        <f t="shared" si="2"/>
         <v>0.99999988974763232</v>
       </c>
       <c r="N38">
-        <f>N37+D38</f>
+        <f t="shared" si="1"/>
         <v>16374999</v>
       </c>
       <c r="O38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99999993893129768</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.99999982867893678</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="F39" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="G39">
         <f>SUM(G2:G37)</f>
@@ -5815,7 +5444,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5825,1262 +5454,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F73C74-20E1-4CF2-8AE1-F98B6BF5F0A1}">
-  <dimension ref="A1:X68"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="5" max="5" width="13.125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1">
-        <v>1000000</v>
-      </c>
-      <c r="V1" t="s">
-        <v>43</v>
-      </c>
-      <c r="W1" t="s">
-        <v>44</v>
-      </c>
-      <c r="X1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2">
-        <v>1000000000</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>113608</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2">
-        <v>10000000</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="R2" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="S2" s="2">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3">
-        <v>1</v>
-      </c>
-      <c r="W2" s="3"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3">
-        <v>1000000000</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>113608</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3">
-        <v>100000000</v>
-      </c>
-      <c r="N3">
-        <v>1000</v>
-      </c>
-      <c r="O3">
-        <f>$N3*O$2</f>
-        <v>200</v>
-      </c>
-      <c r="P3">
-        <f t="shared" ref="P3:S3" si="0">$N3*P$2</f>
-        <v>400</v>
-      </c>
-      <c r="Q3">
-        <f t="shared" si="0"/>
-        <v>600</v>
-      </c>
-      <c r="R3">
-        <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-      <c r="S3">
-        <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="V3">
-        <v>2</v>
-      </c>
-      <c r="W3">
-        <v>1055</v>
-      </c>
-      <c r="X3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4">
-        <v>1500000000</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>250501608</v>
-      </c>
-      <c r="F4">
-        <v>1000</v>
-      </c>
-      <c r="G4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4">
-        <v>62</v>
-      </c>
-      <c r="J4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4">
-        <v>1000000000</v>
-      </c>
-      <c r="O4">
-        <f>$C$4+O3*$E$4</f>
-        <v>51600321600</v>
-      </c>
-      <c r="P4">
-        <f t="shared" ref="P4:S4" si="1">$C$4+P3*$E$4</f>
-        <v>101700643200</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" si="1"/>
-        <v>151800964800</v>
-      </c>
-      <c r="R4">
-        <f t="shared" si="1"/>
-        <v>201901286400</v>
-      </c>
-      <c r="S4">
-        <f t="shared" si="1"/>
-        <v>252001608000</v>
-      </c>
-      <c r="V4">
-        <v>10</v>
-      </c>
-      <c r="W4">
-        <v>855</v>
-      </c>
-      <c r="X4">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5">
-        <v>1500000000</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>21501608</v>
-      </c>
-      <c r="F5">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5">
-        <v>136</v>
-      </c>
-      <c r="J5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5">
-        <v>10000000000</v>
-      </c>
-      <c r="O5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P5" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>62</v>
-      </c>
-      <c r="R5" t="s">
-        <v>63</v>
-      </c>
-      <c r="S5" t="s">
-        <v>64</v>
-      </c>
-      <c r="T5" t="s">
-        <v>65</v>
-      </c>
-      <c r="V5" t="s">
-        <v>66</v>
-      </c>
-      <c r="W5">
-        <v>1216</v>
-      </c>
-      <c r="X5">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6">
-        <v>251751106392</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>800000000</v>
-      </c>
-      <c r="F6">
-        <v>1000</v>
-      </c>
-      <c r="G6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6">
-        <v>188</v>
-      </c>
-      <c r="J6" t="s">
-        <v>70</v>
-      </c>
-      <c r="K6">
-        <v>100000000000</v>
-      </c>
-      <c r="N6">
-        <v>5000</v>
-      </c>
-      <c r="O6">
-        <f>$N6*O$2</f>
-        <v>1000</v>
-      </c>
-      <c r="P6">
-        <f>$N6*P$2</f>
-        <v>2000</v>
-      </c>
-      <c r="Q6">
-        <f>$N6*Q$2</f>
-        <v>3000</v>
-      </c>
-      <c r="R6">
-        <f>$N6*R$2</f>
-        <v>4000</v>
-      </c>
-      <c r="S6">
-        <f>$N6*S$2</f>
-        <v>5000</v>
-      </c>
-      <c r="W6">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7">
-        <v>108986538392</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>420000000</v>
-      </c>
-      <c r="F7">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7">
-        <v>405</v>
-      </c>
-      <c r="J7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7">
-        <v>1000000000000</v>
-      </c>
-      <c r="O7">
-        <f>$C$4+O6*$E$5</f>
-        <v>23001608000</v>
-      </c>
-      <c r="P7">
-        <f t="shared" ref="P7:S7" si="2">$C$4+P6*$E$5</f>
-        <v>44503216000</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="2"/>
-        <v>66004824000</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="2"/>
-        <v>87506432000</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>109008040000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="H8">
-        <v>250</v>
-      </c>
-      <c r="J8" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8">
-        <v>10000000000000</v>
-      </c>
-      <c r="O8" t="s">
-        <v>76</v>
-      </c>
-      <c r="P8" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>78</v>
-      </c>
-      <c r="R8" t="s">
-        <v>79</v>
-      </c>
-      <c r="S8" t="s">
-        <v>80</v>
-      </c>
-      <c r="T8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="E9">
-        <v>630004020000000</v>
-      </c>
-      <c r="H9">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11">
-        <f>C4+999*E4</f>
-        <v>251751106392</v>
-      </c>
-      <c r="E11">
-        <f>1000/2*(2*C6+(1000)*E6)</f>
-        <v>651751106392000</v>
-      </c>
-      <c r="H11">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12">
-        <f>C5+4999*E5</f>
-        <v>108986538392</v>
-      </c>
-      <c r="E12">
-        <f>5000/2*(2*C7+(5000)*E7)</f>
-        <v>5794932691960000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="J17" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17">
-        <v>100000000000000</v>
-      </c>
-      <c r="M17" t="s">
-        <v>52</v>
-      </c>
-      <c r="N17">
-        <f>C4+1000*E4</f>
-        <v>252001608000</v>
-      </c>
-      <c r="O17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C18">
-        <f>1000/2*(C4+999*E4)</f>
-        <v>125875553196000</v>
-      </c>
-      <c r="E18">
-        <v>252001608000</v>
-      </c>
-      <c r="M18" t="s">
-        <v>56</v>
-      </c>
-      <c r="N18">
-        <f>C4+5000*E5</f>
-        <v>109008040000</v>
-      </c>
-      <c r="O18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C19">
-        <f>5000/2*(C5+5000*E5)</f>
-        <v>272520100000000</v>
-      </c>
-      <c r="E19">
-        <v>109008040000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C20">
-        <f>1000/2*(C6+999*E6)</f>
-        <v>525475553196000</v>
-      </c>
-      <c r="D20">
-        <f>C20/C18</f>
-        <v>4.1745640027320112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C21">
-        <f>5000/2*(C7+5000*E7)</f>
-        <v>5522466345980000</v>
-      </c>
-      <c r="D21">
-        <f>C21/C19</f>
-        <v>20.264436810275647</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="G23" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E24" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24">
-        <v>67</v>
-      </c>
-      <c r="G24">
-        <v>9</v>
-      </c>
-      <c r="H24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E25" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25">
-        <v>20</v>
-      </c>
-      <c r="G25">
-        <v>9</v>
-      </c>
-      <c r="H25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26">
-        <v>1200</v>
-      </c>
-      <c r="E26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26">
-        <v>10</v>
-      </c>
-      <c r="G26">
-        <v>9</v>
-      </c>
-      <c r="H26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E27" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27">
-        <v>2.4</v>
-      </c>
-      <c r="G27">
-        <v>9</v>
-      </c>
-      <c r="H27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E28" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28">
-        <v>0.5</v>
-      </c>
-      <c r="G28">
-        <v>9</v>
-      </c>
-      <c r="H28">
-        <v>3</v>
-      </c>
-      <c r="R28" t="s">
-        <v>91</v>
-      </c>
-      <c r="S28" t="s">
-        <v>92</v>
-      </c>
-      <c r="T28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E29" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29">
-        <v>0.1</v>
-      </c>
-      <c r="G29">
-        <v>9</v>
-      </c>
-      <c r="H29">
-        <v>3</v>
-      </c>
-      <c r="R29" s="4">
-        <f>H39*1500</f>
-        <v>13500000</v>
-      </c>
-      <c r="S29" s="5">
-        <f>R29/R31*S31</f>
-        <v>4500000</v>
-      </c>
-      <c r="T29" s="6">
-        <f>S29/5.59</f>
-        <v>805008.94454382826</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="R30" t="s">
-        <v>91</v>
-      </c>
-      <c r="S30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="R31">
-        <v>7500</v>
-      </c>
-      <c r="S31">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="I32" t="s">
-        <v>96</v>
-      </c>
-      <c r="J32">
-        <v>3000</v>
-      </c>
-      <c r="K32">
-        <f>J32/2</f>
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="33" spans="5:15" ht="33" x14ac:dyDescent="0.3">
-      <c r="E33" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I33">
-        <v>6</v>
-      </c>
-      <c r="J33">
-        <v>5</v>
-      </c>
-      <c r="K33">
-        <v>4</v>
-      </c>
-      <c r="L33">
-        <v>3</v>
-      </c>
-      <c r="M33">
-        <v>2</v>
-      </c>
-      <c r="N33">
-        <v>1</v>
-      </c>
-      <c r="O33" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E34" s="8">
-        <v>1</v>
-      </c>
-      <c r="F34">
-        <v>67</v>
-      </c>
-      <c r="G34" s="9">
-        <f>F34/100/9</f>
-        <v>7.4444444444444452E-2</v>
-      </c>
-      <c r="H34">
-        <f t="shared" ref="H34:H38" si="3">1/G34</f>
-        <v>13.432835820895521</v>
-      </c>
-      <c r="I34">
-        <f t="shared" ref="I34:N39" si="4">$H34/I$33</f>
-        <v>2.2388059701492535</v>
-      </c>
-      <c r="J34">
-        <f t="shared" si="4"/>
-        <v>2.6865671641791042</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="4"/>
-        <v>3.3582089552238803</v>
-      </c>
-      <c r="L34">
-        <f t="shared" si="4"/>
-        <v>4.4776119402985071</v>
-      </c>
-      <c r="M34">
-        <f t="shared" si="4"/>
-        <v>6.7164179104477606</v>
-      </c>
-      <c r="N34">
-        <f t="shared" si="4"/>
-        <v>13.432835820895521</v>
-      </c>
-      <c r="O34" s="5">
-        <f t="shared" ref="O34:O38" si="5">SUM(I34:N34)</f>
-        <v>32.910447761194028</v>
-      </c>
-    </row>
-    <row r="35" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E35" s="8">
-        <v>2</v>
-      </c>
-      <c r="F35">
-        <v>20</v>
-      </c>
-      <c r="G35" s="9">
-        <f t="shared" ref="G35:G39" si="6">F35/100/9</f>
-        <v>2.2222222222222223E-2</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="3"/>
-        <v>45</v>
-      </c>
-      <c r="I35">
-        <f t="shared" si="4"/>
-        <v>7.5</v>
-      </c>
-      <c r="J35">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="4"/>
-        <v>11.25</v>
-      </c>
-      <c r="L35">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="M35">
-        <f t="shared" si="4"/>
-        <v>22.5</v>
-      </c>
-      <c r="N35">
-        <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="O35" s="5">
-        <f t="shared" si="5"/>
-        <v>110.25</v>
-      </c>
-    </row>
-    <row r="36" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E36" s="8">
-        <v>3</v>
-      </c>
-      <c r="F36">
-        <v>10</v>
-      </c>
-      <c r="G36" s="9">
-        <f t="shared" si="6"/>
-        <v>1.1111111111111112E-2</v>
-      </c>
-      <c r="H36">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="I36">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="J36">
-        <f t="shared" si="4"/>
-        <v>18</v>
-      </c>
-      <c r="K36">
-        <f t="shared" si="4"/>
-        <v>22.5</v>
-      </c>
-      <c r="L36">
-        <f t="shared" si="4"/>
-        <v>30</v>
-      </c>
-      <c r="M36">
-        <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="N36">
-        <f t="shared" si="4"/>
-        <v>90</v>
-      </c>
-      <c r="O36" s="5">
-        <f t="shared" si="5"/>
-        <v>220.5</v>
-      </c>
-    </row>
-    <row r="37" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E37" s="8">
-        <v>4</v>
-      </c>
-      <c r="F37">
-        <v>2.4</v>
-      </c>
-      <c r="G37" s="9">
-        <f t="shared" si="6"/>
-        <v>2.6666666666666666E-3</v>
-      </c>
-      <c r="H37">
-        <f t="shared" si="3"/>
-        <v>375</v>
-      </c>
-      <c r="I37">
-        <f t="shared" si="4"/>
-        <v>62.5</v>
-      </c>
-      <c r="J37">
-        <f t="shared" si="4"/>
-        <v>75</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="4"/>
-        <v>93.75</v>
-      </c>
-      <c r="L37">
-        <f t="shared" si="4"/>
-        <v>125</v>
-      </c>
-      <c r="M37">
-        <f t="shared" si="4"/>
-        <v>187.5</v>
-      </c>
-      <c r="N37">
-        <f t="shared" si="4"/>
-        <v>375</v>
-      </c>
-      <c r="O37" s="5">
-        <f t="shared" si="5"/>
-        <v>918.75</v>
-      </c>
-    </row>
-    <row r="38" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E38" s="10">
-        <v>5</v>
-      </c>
-      <c r="F38">
-        <v>0.5</v>
-      </c>
-      <c r="G38" s="9">
-        <f t="shared" si="6"/>
-        <v>5.5555555555555556E-4</v>
-      </c>
-      <c r="H38">
-        <f t="shared" si="3"/>
-        <v>1800</v>
-      </c>
-      <c r="I38">
-        <f t="shared" si="4"/>
-        <v>300</v>
-      </c>
-      <c r="J38">
-        <f t="shared" si="4"/>
-        <v>360</v>
-      </c>
-      <c r="K38">
-        <f t="shared" si="4"/>
-        <v>450</v>
-      </c>
-      <c r="L38">
-        <f t="shared" si="4"/>
-        <v>600</v>
-      </c>
-      <c r="M38">
-        <f t="shared" si="4"/>
-        <v>900</v>
-      </c>
-      <c r="N38">
-        <f t="shared" si="4"/>
-        <v>1800</v>
-      </c>
-      <c r="O38" s="5">
-        <f t="shared" si="5"/>
-        <v>4410</v>
-      </c>
-    </row>
-    <row r="39" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E39" s="10">
-        <v>6</v>
-      </c>
-      <c r="F39">
-        <v>0.1</v>
-      </c>
-      <c r="G39" s="9">
-        <f t="shared" si="6"/>
-        <v>1.1111111111111112E-4</v>
-      </c>
-      <c r="H39">
-        <f>1/G39</f>
-        <v>9000</v>
-      </c>
-      <c r="I39">
-        <f>$H39/I$33</f>
-        <v>1500</v>
-      </c>
-      <c r="J39">
-        <f t="shared" si="4"/>
-        <v>1800</v>
-      </c>
-      <c r="K39">
-        <f t="shared" si="4"/>
-        <v>2250</v>
-      </c>
-      <c r="L39">
-        <f t="shared" si="4"/>
-        <v>3000</v>
-      </c>
-      <c r="M39">
-        <f t="shared" si="4"/>
-        <v>4500</v>
-      </c>
-      <c r="N39">
-        <f t="shared" si="4"/>
-        <v>9000</v>
-      </c>
-      <c r="O39" s="5">
-        <f t="shared" ref="O39:O41" si="7">SUM(I39:N39)</f>
-        <v>22050</v>
-      </c>
-    </row>
-    <row r="40" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="H40" t="s">
-        <v>91</v>
-      </c>
-      <c r="I40" s="4">
-        <f>I39*$K32</f>
-        <v>2250000</v>
-      </c>
-      <c r="J40" s="4">
-        <f t="shared" ref="J40:N40" si="8">J39*$K32</f>
-        <v>2700000</v>
-      </c>
-      <c r="K40" s="4">
-        <f t="shared" si="8"/>
-        <v>3375000</v>
-      </c>
-      <c r="L40" s="4">
-        <f t="shared" si="8"/>
-        <v>4500000</v>
-      </c>
-      <c r="M40" s="4">
-        <f t="shared" si="8"/>
-        <v>6750000</v>
-      </c>
-      <c r="N40" s="4">
-        <f t="shared" si="8"/>
-        <v>13500000</v>
-      </c>
-      <c r="O40" s="5">
-        <f t="shared" si="7"/>
-        <v>33075000</v>
-      </c>
-    </row>
-    <row r="41" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="H41" t="s">
-        <v>92</v>
-      </c>
-      <c r="I41" s="4">
-        <f>I40/$R31*$S31</f>
-        <v>750000</v>
-      </c>
-      <c r="J41" s="4">
-        <f t="shared" ref="J41:N41" si="9">J40/$R31*$S31</f>
-        <v>900000</v>
-      </c>
-      <c r="K41" s="4">
-        <f t="shared" si="9"/>
-        <v>1125000</v>
-      </c>
-      <c r="L41" s="4">
-        <f t="shared" si="9"/>
-        <v>1500000</v>
-      </c>
-      <c r="M41" s="4">
-        <f t="shared" si="9"/>
-        <v>2250000</v>
-      </c>
-      <c r="N41" s="4">
-        <f t="shared" si="9"/>
-        <v>4500000</v>
-      </c>
-      <c r="O41" s="5">
-        <f t="shared" si="7"/>
-        <v>11025000</v>
-      </c>
-    </row>
-    <row r="42" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="H42" t="s">
-        <v>101</v>
-      </c>
-      <c r="I42" s="4">
-        <f>I41/5.59</f>
-        <v>134168.15742397137</v>
-      </c>
-      <c r="J42" s="4">
-        <f t="shared" ref="J42:N42" si="10">J41/5.59</f>
-        <v>161001.78890876565</v>
-      </c>
-      <c r="K42" s="4">
-        <f t="shared" si="10"/>
-        <v>201252.23613595706</v>
-      </c>
-      <c r="L42" s="4">
-        <f t="shared" si="10"/>
-        <v>268336.31484794273</v>
-      </c>
-      <c r="M42" s="4">
-        <f t="shared" si="10"/>
-        <v>402504.47227191413</v>
-      </c>
-      <c r="N42" s="4">
-        <f t="shared" si="10"/>
-        <v>805008.94454382826</v>
-      </c>
-      <c r="O42" s="5">
-        <f>SUM(I42:N42)</f>
-        <v>1972271.9141323792</v>
-      </c>
-    </row>
-    <row r="49" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E49" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="50" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E50" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E51" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E52" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E53" t="s">
-        <v>106</v>
-      </c>
-      <c r="L53" t="s">
-        <v>42</v>
-      </c>
-      <c r="M53">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="54" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E54" t="s">
-        <v>107</v>
-      </c>
-      <c r="L54" t="s">
-        <v>48</v>
-      </c>
-      <c r="M54">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="55" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E55" t="s">
-        <v>108</v>
-      </c>
-      <c r="L55" t="s">
-        <v>50</v>
-      </c>
-      <c r="M55">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="56" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E56" t="s">
-        <v>109</v>
-      </c>
-      <c r="L56" t="s">
-        <v>55</v>
-      </c>
-      <c r="M56">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="57" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E57" t="s">
-        <v>110</v>
-      </c>
-      <c r="L57" t="s">
-        <v>59</v>
-      </c>
-      <c r="M57">
-        <v>10000000000</v>
-      </c>
-    </row>
-    <row r="58" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L58" t="s">
-        <v>70</v>
-      </c>
-      <c r="M58">
-        <v>100000000000</v>
-      </c>
-    </row>
-    <row r="59" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L59" t="s">
-        <v>74</v>
-      </c>
-      <c r="M59">
-        <v>1000000000000</v>
-      </c>
-    </row>
-    <row r="60" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L60" t="s">
-        <v>75</v>
-      </c>
-      <c r="M60">
-        <v>10000000000000</v>
-      </c>
-    </row>
-    <row r="61" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L61" t="s">
-        <v>83</v>
-      </c>
-      <c r="M61">
-        <v>100000000000000</v>
-      </c>
-    </row>
-    <row r="63" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E63" t="s">
-        <v>111</v>
-      </c>
-      <c r="F63" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="64" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E64" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="65" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E65" t="s">
-        <v>114</v>
-      </c>
-      <c r="F65" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="66" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E66" t="s">
-        <v>116</v>
-      </c>
-      <c r="F66">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="67" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E67" t="s">
-        <v>117</v>
-      </c>
-      <c r="G67" t="s">
-        <v>118</v>
-      </c>
-      <c r="H67" t="s">
-        <v>119</v>
-      </c>
-      <c r="I67" t="s">
-        <v>95</v>
-      </c>
-      <c r="J67" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E68" s="11">
-        <v>12.37</v>
-      </c>
-      <c r="G68">
-        <v>569</v>
-      </c>
-      <c r="H68">
-        <v>41.8</v>
-      </c>
-      <c r="I68">
-        <v>2000</v>
-      </c>
-      <c r="J68">
-        <v>34560</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>